--- a/INCREMENTO 2/Backlog review 2.xlsx
+++ b/INCREMENTO 2/Backlog review 2.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="525">
   <si>
     <t>incremento 1</t>
   </si>
@@ -602,6 +602,12 @@
     <t>Reportando cantidad de NNA satisfechos por categoria</t>
   </si>
   <si>
+    <t>Diseñar diagrma de secuencia</t>
+  </si>
+  <si>
+    <t>Diseñar el diagrama de secuencia para los eventos de reporte.</t>
+  </si>
+  <si>
     <t>Diseñar interfaz del módulo</t>
   </si>
   <si>
@@ -692,6 +698,9 @@
     <t>Reporte de cantidad de respuestas por programa</t>
   </si>
   <si>
+    <t>Diseñar el diagrama de secuancia que representa los eventos de reporte de cantidad de respuestas</t>
+  </si>
+  <si>
     <t>Diseñar interfaz</t>
   </si>
   <si>
@@ -725,6 +734,9 @@
     <t>Reportando documento existentes e inexistentes</t>
   </si>
   <si>
+    <t>Diseñar el diagrama de secuancia que representa los eventos de reporte de exixtencia e inexistencia</t>
+  </si>
+  <si>
     <t>Diseñar interface de existencias</t>
   </si>
   <si>
@@ -785,9 +797,18 @@
     <t>Registrar auditoria en base de datos</t>
   </si>
   <si>
+    <t>Evitar error de encuesta</t>
+  </si>
+  <si>
+    <t>Implementar un comprovante para asegurar el envio de la infomación que escribe el usuario que realiza la encuesta a la base de datos, en caso cotrario debe mostrar un mensaje de tarea incompleta, para que el usuario vuelva a intentar enviar la encuesta a ser guardada mediante un boton/enlace disponible luego del error.</t>
+  </si>
+  <si>
     <t>Etiquetado de documentos</t>
   </si>
   <si>
+    <t>Diseñar el diagrama de secuancia que representa los eventos de etiquetado</t>
+  </si>
+  <si>
     <t>Diseñar formulario de etiquetado</t>
   </si>
   <si>
@@ -821,6 +842,9 @@
     <t>Favoritos o destacados</t>
   </si>
   <si>
+    <t>Diseñar el diagrama de secuancia que representa los eventos de los elementos favoritos</t>
+  </si>
+  <si>
     <t>Diseñar la interfaz de favoritos</t>
   </si>
   <si>
@@ -848,6 +872,12 @@
     <t>Link de acceso a documentos</t>
   </si>
   <si>
+    <t>Diseño diagrama de secuencia</t>
+  </si>
+  <si>
+    <t>Diseñar el diagrama de secuancia que representa los eventos de los links de acceso</t>
+  </si>
+  <si>
     <t>Diseño de intrefaz de opción</t>
   </si>
   <si>
@@ -875,6 +905,9 @@
     <t>Comentarios en documentos</t>
   </si>
   <si>
+    <t>Diseñar el diagrama de secuancia que representa los eventos de la seccion de comentarios en los documentos</t>
+  </si>
+  <si>
     <t>Diseñar sección de comentarios</t>
   </si>
   <si>
@@ -936,6 +969,12 @@
   </si>
   <si>
     <t>Reportando por cantidad de respuestas por programa (auditoria)</t>
+  </si>
+  <si>
+    <t>Diseñar diagrama  de secuencia</t>
+  </si>
+  <si>
+    <t>Diseñar el diagrama de secuancia que representa los eventos de los reportes</t>
   </si>
   <si>
     <t>Diseñar componente</t>
@@ -2153,80 +2192,80 @@
     <xf borderId="5" fillId="10" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="11" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="11" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="12" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="12" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="12" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="12" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="8" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="13" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="13" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="7" fillId="13" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="13" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="13" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="13" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="13" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="13" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="11" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="11" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="11" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="6" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="9" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="5" fillId="9" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="13" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="11" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="11" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="9" fillId="11" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="12" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="12" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="12" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="9" fillId="12" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="8" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="13" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="13" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="13" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="7" fillId="13" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="13" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="13" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="13" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="13" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="9" fillId="13" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="11" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="11" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="11" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="6" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="9" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="5" fillId="9" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="7" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
@@ -5296,7 +5335,9 @@
         <v>135</v>
       </c>
       <c r="C86" s="84"/>
-      <c r="D86" s="84"/>
+      <c r="D86" s="11">
+        <v>6.0</v>
+      </c>
       <c r="E86" s="84" t="s">
         <v>65</v>
       </c>
@@ -5321,7 +5362,9 @@
         <v>137</v>
       </c>
       <c r="C87" s="84"/>
-      <c r="D87" s="84"/>
+      <c r="D87" s="11">
+        <v>3.0</v>
+      </c>
       <c r="E87" s="84" t="s">
         <v>65</v>
       </c>
@@ -5346,7 +5389,9 @@
         <v>139</v>
       </c>
       <c r="C88" s="84"/>
-      <c r="D88" s="84"/>
+      <c r="D88" s="11">
+        <v>4.0</v>
+      </c>
       <c r="E88" s="84" t="s">
         <v>65</v>
       </c>
@@ -5371,7 +5416,9 @@
         <v>51</v>
       </c>
       <c r="C89" s="84"/>
-      <c r="D89" s="84"/>
+      <c r="D89" s="11">
+        <v>1.0</v>
+      </c>
       <c r="E89" s="84" t="s">
         <v>65</v>
       </c>
@@ -5396,7 +5443,9 @@
         <v>142</v>
       </c>
       <c r="C90" s="84"/>
-      <c r="D90" s="84"/>
+      <c r="D90" s="11">
+        <v>1.0</v>
+      </c>
       <c r="E90" s="84" t="s">
         <v>65</v>
       </c>
@@ -5477,7 +5526,9 @@
       <c r="C93" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="D93" s="90"/>
+      <c r="D93" s="18">
+        <v>6.0</v>
+      </c>
       <c r="E93" s="18" t="s">
         <v>146</v>
       </c>
@@ -5506,7 +5557,9 @@
       <c r="C94" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="D94" s="90"/>
+      <c r="D94" s="18">
+        <v>2.0</v>
+      </c>
       <c r="E94" s="18" t="s">
         <v>146</v>
       </c>
@@ -5535,7 +5588,9 @@
       <c r="C95" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="D95" s="90"/>
+      <c r="D95" s="18">
+        <v>3.0</v>
+      </c>
       <c r="E95" s="18" t="s">
         <v>146</v>
       </c>
@@ -5564,7 +5619,9 @@
       <c r="C96" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="D96" s="90"/>
+      <c r="D96" s="18">
+        <v>1.0</v>
+      </c>
       <c r="E96" s="18" t="s">
         <v>146</v>
       </c>
@@ -5593,7 +5650,9 @@
       <c r="C97" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="D97" s="90"/>
+      <c r="D97" s="18">
+        <v>3.0</v>
+      </c>
       <c r="E97" s="18" t="s">
         <v>146</v>
       </c>
@@ -5674,7 +5733,9 @@
         <v>135</v>
       </c>
       <c r="C100" s="96"/>
-      <c r="D100" s="96"/>
+      <c r="D100" s="29">
+        <v>6.0</v>
+      </c>
       <c r="E100" s="96" t="s">
         <v>65</v>
       </c>
@@ -5699,7 +5760,9 @@
         <v>158</v>
       </c>
       <c r="C101" s="96"/>
-      <c r="D101" s="96"/>
+      <c r="D101" s="29">
+        <v>4.0</v>
+      </c>
       <c r="E101" s="96" t="s">
         <v>65</v>
       </c>
@@ -5724,7 +5787,9 @@
         <v>160</v>
       </c>
       <c r="C102" s="96"/>
-      <c r="D102" s="96"/>
+      <c r="D102" s="29">
+        <v>2.0</v>
+      </c>
       <c r="E102" s="96" t="s">
         <v>65</v>
       </c>
@@ -5749,7 +5814,9 @@
         <v>162</v>
       </c>
       <c r="C103" s="96"/>
-      <c r="D103" s="96"/>
+      <c r="D103" s="29">
+        <v>3.0</v>
+      </c>
       <c r="E103" s="96" t="s">
         <v>65</v>
       </c>
@@ -5774,7 +5841,9 @@
         <v>164</v>
       </c>
       <c r="C104" s="96"/>
-      <c r="D104" s="96"/>
+      <c r="D104" s="29">
+        <v>4.0</v>
+      </c>
       <c r="E104" s="96" t="s">
         <v>65</v>
       </c>
@@ -5853,7 +5922,9 @@
         <v>135</v>
       </c>
       <c r="C107" s="101"/>
-      <c r="D107" s="101"/>
+      <c r="D107" s="35">
+        <v>5.0</v>
+      </c>
       <c r="E107" s="101" t="s">
         <v>65</v>
       </c>
@@ -5878,7 +5949,9 @@
         <v>168</v>
       </c>
       <c r="C108" s="101"/>
-      <c r="D108" s="101"/>
+      <c r="D108" s="35">
+        <v>3.0</v>
+      </c>
       <c r="E108" s="101" t="s">
         <v>65</v>
       </c>
@@ -5903,7 +5976,9 @@
         <v>170</v>
       </c>
       <c r="C109" s="101"/>
-      <c r="D109" s="101"/>
+      <c r="D109" s="35">
+        <v>3.0</v>
+      </c>
       <c r="E109" s="101" t="s">
         <v>65</v>
       </c>
@@ -5928,7 +6003,9 @@
         <v>172</v>
       </c>
       <c r="C110" s="101"/>
-      <c r="D110" s="101"/>
+      <c r="D110" s="35">
+        <v>4.0</v>
+      </c>
       <c r="E110" s="101" t="s">
         <v>65</v>
       </c>
@@ -5953,7 +6030,9 @@
         <v>174</v>
       </c>
       <c r="C111" s="101"/>
-      <c r="D111" s="101"/>
+      <c r="D111" s="35">
+        <v>2.0</v>
+      </c>
       <c r="E111" s="101" t="s">
         <v>65</v>
       </c>
@@ -6032,7 +6111,9 @@
         <v>135</v>
       </c>
       <c r="C114" s="105"/>
-      <c r="D114" s="105"/>
+      <c r="D114" s="42">
+        <v>9.0</v>
+      </c>
       <c r="E114" s="105" t="s">
         <v>65</v>
       </c>
@@ -6057,7 +6138,9 @@
         <v>178</v>
       </c>
       <c r="C115" s="105"/>
-      <c r="D115" s="105"/>
+      <c r="D115" s="42">
+        <v>4.0</v>
+      </c>
       <c r="E115" s="105" t="s">
         <v>65</v>
       </c>
@@ -6082,7 +6165,9 @@
         <v>180</v>
       </c>
       <c r="C116" s="105"/>
-      <c r="D116" s="105"/>
+      <c r="D116" s="42">
+        <v>3.0</v>
+      </c>
       <c r="E116" s="105" t="s">
         <v>65</v>
       </c>
@@ -6107,7 +6192,9 @@
         <v>182</v>
       </c>
       <c r="C117" s="105"/>
-      <c r="D117" s="105"/>
+      <c r="D117" s="42">
+        <v>2.0</v>
+      </c>
       <c r="E117" s="105" t="s">
         <v>65</v>
       </c>
@@ -6132,7 +6219,9 @@
         <v>184</v>
       </c>
       <c r="C118" s="105"/>
-      <c r="D118" s="105"/>
+      <c r="D118" s="42">
+        <v>3.0</v>
+      </c>
       <c r="E118" s="105" t="s">
         <v>65</v>
       </c>
@@ -6211,7 +6300,9 @@
         <v>135</v>
       </c>
       <c r="C121" s="111"/>
-      <c r="D121" s="111"/>
+      <c r="D121" s="49">
+        <v>8.0</v>
+      </c>
       <c r="E121" s="111" t="s">
         <v>65</v>
       </c>
@@ -6236,7 +6327,9 @@
         <v>188</v>
       </c>
       <c r="C122" s="111"/>
-      <c r="D122" s="111"/>
+      <c r="D122" s="49">
+        <v>5.0</v>
+      </c>
       <c r="E122" s="111" t="s">
         <v>65</v>
       </c>
@@ -6261,7 +6354,9 @@
         <v>190</v>
       </c>
       <c r="C123" s="111"/>
-      <c r="D123" s="111"/>
+      <c r="D123" s="49">
+        <v>3.0</v>
+      </c>
       <c r="E123" s="111" t="s">
         <v>65</v>
       </c>
@@ -6286,7 +6381,9 @@
         <v>190</v>
       </c>
       <c r="C124" s="111"/>
-      <c r="D124" s="111"/>
+      <c r="D124" s="49">
+        <v>3.0</v>
+      </c>
       <c r="E124" s="111" t="s">
         <v>65</v>
       </c>
@@ -6311,7 +6408,9 @@
         <v>193</v>
       </c>
       <c r="C125" s="111"/>
-      <c r="D125" s="111"/>
+      <c r="D125" s="49">
+        <v>4.0</v>
+      </c>
       <c r="E125" s="111" t="s">
         <v>65</v>
       </c>
@@ -6390,7 +6489,9 @@
         <v>196</v>
       </c>
       <c r="C128" s="116"/>
-      <c r="D128" s="116"/>
+      <c r="D128" s="58">
+        <v>9.0</v>
+      </c>
       <c r="E128" s="58" t="s">
         <v>65</v>
       </c>
@@ -6408,14 +6509,16 @@
       <c r="K128" s="118"/>
     </row>
     <row r="129">
-      <c r="A129" s="62">
+      <c r="A129" s="57">
         <v>14.0</v>
       </c>
       <c r="B129" s="58" t="s">
         <v>198</v>
       </c>
       <c r="C129" s="116"/>
-      <c r="D129" s="116"/>
+      <c r="D129" s="58">
+        <v>7.0</v>
+      </c>
       <c r="E129" s="58" t="s">
         <v>65</v>
       </c>
@@ -6440,7 +6543,9 @@
         <v>200</v>
       </c>
       <c r="C130" s="116"/>
-      <c r="D130" s="116"/>
+      <c r="D130" s="58">
+        <v>6.0</v>
+      </c>
       <c r="E130" s="58" t="s">
         <v>65</v>
       </c>
@@ -6465,7 +6570,9 @@
         <v>202</v>
       </c>
       <c r="C131" s="116"/>
-      <c r="D131" s="116"/>
+      <c r="D131" s="58">
+        <v>3.0</v>
+      </c>
       <c r="E131" s="58" t="s">
         <v>65</v>
       </c>
@@ -6490,11 +6597,13 @@
         <v>204</v>
       </c>
       <c r="C132" s="116"/>
-      <c r="D132" s="116"/>
+      <c r="D132" s="58">
+        <v>2.0</v>
+      </c>
       <c r="E132" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="F132" s="64" t="s">
+      <c r="F132" s="59" t="s">
         <v>205</v>
       </c>
       <c r="G132" s="117">
@@ -6508,116 +6617,116 @@
       <c r="K132" s="118"/>
     </row>
     <row r="133">
-      <c r="A133" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B133" s="4"/>
-      <c r="C133" s="4"/>
-      <c r="D133" s="4"/>
-      <c r="E133" s="4"/>
-      <c r="F133" s="5"/>
-      <c r="G133" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H133" s="5"/>
-      <c r="I133" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J133" s="5"/>
-      <c r="K133" s="5"/>
+      <c r="A133" s="62">
+        <v>14.0</v>
+      </c>
+      <c r="B133" s="58" t="s">
+        <v>206</v>
+      </c>
+      <c r="C133" s="116"/>
+      <c r="D133" s="58">
+        <v>3.0</v>
+      </c>
+      <c r="E133" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="F133" s="64" t="s">
+        <v>207</v>
+      </c>
+      <c r="G133" s="117">
+        <v>45901.0</v>
+      </c>
+      <c r="H133" s="118"/>
+      <c r="I133" s="117">
+        <v>45901.0</v>
+      </c>
+      <c r="J133" s="118"/>
+      <c r="K133" s="118"/>
     </row>
     <row r="134">
       <c r="A134" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B134" s="4"/>
+      <c r="C134" s="4"/>
+      <c r="D134" s="4"/>
+      <c r="E134" s="4"/>
+      <c r="F134" s="5"/>
+      <c r="G134" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H134" s="5"/>
+      <c r="I134" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J134" s="5"/>
+      <c r="K134" s="5"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B134" s="4" t="s">
+      <c r="B135" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C134" s="4" t="s">
+      <c r="C135" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D134" s="4" t="s">
+      <c r="D135" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E134" s="4" t="s">
+      <c r="E135" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F134" s="7" t="s">
+      <c r="F135" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G134" s="6" t="s">
+      <c r="G135" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H134" s="5" t="s">
+      <c r="H135" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I134" s="6" t="s">
+      <c r="I135" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J134" s="5" t="s">
+      <c r="J135" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K134" s="8" t="s">
+      <c r="K135" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="65" t="s">
-        <v>206</v>
-      </c>
-      <c r="B135" s="66" t="s">
+    <row r="136">
+      <c r="A136" s="65" t="s">
+        <v>208</v>
+      </c>
+      <c r="B136" s="66" t="s">
         <v>135</v>
-      </c>
-      <c r="C135" s="66" t="s">
-        <v>145</v>
-      </c>
-      <c r="D135" s="119"/>
-      <c r="E135" s="66" t="s">
-        <v>146</v>
-      </c>
-      <c r="F135" s="67" t="s">
-        <v>207</v>
-      </c>
-      <c r="G135" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H135" s="121"/>
-      <c r="I135" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="J135" s="70">
-        <v>45912.0</v>
-      </c>
-      <c r="K135" s="121"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="71">
-        <v>15.0</v>
-      </c>
-      <c r="B136" s="66" t="s">
-        <v>208</v>
       </c>
       <c r="C136" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="D136" s="119"/>
+      <c r="D136" s="66">
+        <v>7.0</v>
+      </c>
       <c r="E136" s="66" t="s">
         <v>146</v>
       </c>
       <c r="F136" s="67" t="s">
         <v>209</v>
       </c>
-      <c r="G136" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H136" s="121"/>
-      <c r="I136" s="120">
+      <c r="G136" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H136" s="120"/>
+      <c r="I136" s="119">
         <v>45901.0</v>
       </c>
       <c r="J136" s="70">
         <v>45912.0</v>
       </c>
-      <c r="K136" s="121"/>
+      <c r="K136" s="120"/>
     </row>
     <row r="137">
       <c r="A137" s="71">
@@ -6629,24 +6738,26 @@
       <c r="C137" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="D137" s="119"/>
+      <c r="D137" s="66">
+        <v>4.0</v>
+      </c>
       <c r="E137" s="66" t="s">
         <v>146</v>
       </c>
       <c r="F137" s="67" t="s">
         <v>211</v>
       </c>
-      <c r="G137" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H137" s="121"/>
-      <c r="I137" s="120">
+      <c r="G137" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H137" s="120"/>
+      <c r="I137" s="119">
         <v>45901.0</v>
       </c>
       <c r="J137" s="70">
         <v>45912.0</v>
       </c>
-      <c r="K137" s="121"/>
+      <c r="K137" s="120"/>
     </row>
     <row r="138">
       <c r="A138" s="71">
@@ -6658,24 +6769,26 @@
       <c r="C138" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="D138" s="119"/>
+      <c r="D138" s="66">
+        <v>5.0</v>
+      </c>
       <c r="E138" s="66" t="s">
         <v>146</v>
       </c>
       <c r="F138" s="67" t="s">
         <v>213</v>
       </c>
-      <c r="G138" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H138" s="121"/>
-      <c r="I138" s="120">
+      <c r="G138" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H138" s="120"/>
+      <c r="I138" s="119">
         <v>45901.0</v>
       </c>
       <c r="J138" s="70">
         <v>45912.0</v>
       </c>
-      <c r="K138" s="121"/>
+      <c r="K138" s="120"/>
     </row>
     <row r="139">
       <c r="A139" s="71">
@@ -6687,113 +6800,123 @@
       <c r="C139" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="D139" s="119"/>
+      <c r="D139" s="66">
+        <v>3.0</v>
+      </c>
       <c r="E139" s="66" t="s">
         <v>146</v>
       </c>
-      <c r="F139" s="122" t="s">
+      <c r="F139" s="67" t="s">
         <v>215</v>
       </c>
-      <c r="G139" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H139" s="121"/>
-      <c r="I139" s="120">
+      <c r="G139" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H139" s="120"/>
+      <c r="I139" s="119">
         <v>45901.0</v>
       </c>
       <c r="J139" s="70">
         <v>45912.0</v>
       </c>
-      <c r="K139" s="121"/>
+      <c r="K139" s="120"/>
     </row>
     <row r="140">
-      <c r="A140" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B140" s="4"/>
-      <c r="C140" s="4"/>
-      <c r="D140" s="4"/>
-      <c r="E140" s="4"/>
-      <c r="F140" s="5"/>
-      <c r="G140" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H140" s="5"/>
-      <c r="I140" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J140" s="5"/>
-      <c r="K140" s="5"/>
+      <c r="A140" s="71">
+        <v>15.0</v>
+      </c>
+      <c r="B140" s="66" t="s">
+        <v>216</v>
+      </c>
+      <c r="C140" s="66" t="s">
+        <v>145</v>
+      </c>
+      <c r="D140" s="66">
+        <v>3.0</v>
+      </c>
+      <c r="E140" s="66" t="s">
+        <v>146</v>
+      </c>
+      <c r="F140" s="121" t="s">
+        <v>217</v>
+      </c>
+      <c r="G140" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H140" s="120"/>
+      <c r="I140" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="J140" s="70">
+        <v>45912.0</v>
+      </c>
+      <c r="K140" s="120"/>
     </row>
     <row r="141">
       <c r="A141" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B141" s="4"/>
+      <c r="C141" s="4"/>
+      <c r="D141" s="4"/>
+      <c r="E141" s="4"/>
+      <c r="F141" s="5"/>
+      <c r="G141" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H141" s="5"/>
+      <c r="I141" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J141" s="5"/>
+      <c r="K141" s="5"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B141" s="4" t="s">
+      <c r="B142" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C141" s="4" t="s">
+      <c r="C142" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D141" s="4" t="s">
+      <c r="D142" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E141" s="4" t="s">
+      <c r="E142" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F141" s="7" t="s">
+      <c r="F142" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G141" s="6" t="s">
+      <c r="G142" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H141" s="5" t="s">
+      <c r="H142" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I141" s="6" t="s">
+      <c r="I142" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J141" s="5" t="s">
+      <c r="J142" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K141" s="8" t="s">
+      <c r="K142" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="B142" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="C142" s="84"/>
-      <c r="D142" s="84"/>
-      <c r="E142" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F142" s="12" t="s">
+    <row r="143">
+      <c r="A143" s="11" t="s">
         <v>218</v>
-      </c>
-      <c r="G142" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="H142" s="82"/>
-      <c r="I142" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="J142" s="82"/>
-      <c r="K142" s="82"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="72">
-        <v>17.0</v>
       </c>
       <c r="B143" s="10" t="s">
         <v>219</v>
       </c>
       <c r="C143" s="84"/>
-      <c r="D143" s="84"/>
+      <c r="D143" s="11">
+        <v>7.0</v>
+      </c>
       <c r="E143" s="11" t="s">
         <v>65</v>
       </c>
@@ -6818,7 +6941,9 @@
         <v>221</v>
       </c>
       <c r="C144" s="84"/>
-      <c r="D144" s="84"/>
+      <c r="D144" s="11">
+        <v>7.0</v>
+      </c>
       <c r="E144" s="11" t="s">
         <v>65</v>
       </c>
@@ -6843,7 +6968,9 @@
         <v>223</v>
       </c>
       <c r="C145" s="84"/>
-      <c r="D145" s="84"/>
+      <c r="D145" s="11">
+        <v>6.0</v>
+      </c>
       <c r="E145" s="11" t="s">
         <v>65</v>
       </c>
@@ -6861,98 +6988,102 @@
       <c r="K145" s="82"/>
     </row>
     <row r="146">
-      <c r="A146" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B146" s="4"/>
-      <c r="C146" s="4"/>
-      <c r="D146" s="4"/>
-      <c r="E146" s="4"/>
-      <c r="F146" s="5"/>
-      <c r="G146" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H146" s="5"/>
-      <c r="I146" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J146" s="5"/>
-      <c r="K146" s="5"/>
+      <c r="A146" s="72">
+        <v>17.0</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="C146" s="84"/>
+      <c r="D146" s="11">
+        <v>4.0</v>
+      </c>
+      <c r="E146" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F146" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="G146" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="H146" s="82"/>
+      <c r="I146" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="J146" s="82"/>
+      <c r="K146" s="82"/>
     </row>
     <row r="147">
       <c r="A147" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B147" s="4"/>
+      <c r="C147" s="4"/>
+      <c r="D147" s="4"/>
+      <c r="E147" s="4"/>
+      <c r="F147" s="5"/>
+      <c r="G147" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H147" s="5"/>
+      <c r="I147" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J147" s="5"/>
+      <c r="K147" s="5"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B147" s="4" t="s">
+      <c r="B148" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C147" s="4" t="s">
+      <c r="C148" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D147" s="4" t="s">
+      <c r="D148" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E147" s="4" t="s">
+      <c r="E148" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F147" s="7" t="s">
+      <c r="F148" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G147" s="6" t="s">
+      <c r="G148" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H147" s="5" t="s">
+      <c r="H148" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I147" s="6" t="s">
+      <c r="I148" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J147" s="5" t="s">
+      <c r="J148" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K147" s="8" t="s">
+      <c r="K148" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="17" t="s">
-        <v>225</v>
-      </c>
-      <c r="B148" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="C148" s="90"/>
-      <c r="D148" s="90"/>
-      <c r="E148" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F148" s="19" t="s">
+    <row r="149">
+      <c r="A149" s="17" t="s">
         <v>227</v>
       </c>
-      <c r="G148" s="92">
-        <v>45901.0</v>
-      </c>
-      <c r="H148" s="89"/>
-      <c r="I148" s="92">
-        <v>45901.0</v>
-      </c>
-      <c r="J148" s="89"/>
-      <c r="K148" s="89"/>
-    </row>
-    <row r="149">
-      <c r="A149" s="23">
-        <v>18.0</v>
-      </c>
       <c r="B149" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C149" s="90"/>
+      <c r="D149" s="18">
+        <v>8.0</v>
+      </c>
+      <c r="E149" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F149" s="19" t="s">
         <v>228</v>
-      </c>
-      <c r="C149" s="90"/>
-      <c r="D149" s="90"/>
-      <c r="E149" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F149" s="19" t="s">
-        <v>229</v>
       </c>
       <c r="G149" s="92">
         <v>45901.0</v>
@@ -6965,19 +7096,21 @@
       <c r="K149" s="89"/>
     </row>
     <row r="150">
-      <c r="A150" s="23">
+      <c r="A150" s="17">
         <v>18.0</v>
       </c>
       <c r="B150" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="C150" s="90"/>
+      <c r="D150" s="18">
+        <v>4.0</v>
+      </c>
+      <c r="E150" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F150" s="19" t="s">
         <v>230</v>
-      </c>
-      <c r="C150" s="90"/>
-      <c r="D150" s="90"/>
-      <c r="E150" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F150" s="19" t="s">
-        <v>231</v>
       </c>
       <c r="G150" s="92">
         <v>45901.0</v>
@@ -6994,15 +7127,17 @@
         <v>18.0</v>
       </c>
       <c r="B151" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C151" s="90"/>
+      <c r="D151" s="18">
+        <v>6.0</v>
+      </c>
+      <c r="E151" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F151" s="19" t="s">
         <v>232</v>
-      </c>
-      <c r="C151" s="90"/>
-      <c r="D151" s="90"/>
-      <c r="E151" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F151" s="19" t="s">
-        <v>233</v>
       </c>
       <c r="G151" s="92">
         <v>45901.0</v>
@@ -7019,15 +7154,17 @@
         <v>18.0</v>
       </c>
       <c r="B152" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C152" s="90"/>
+      <c r="D152" s="18">
+        <v>3.0</v>
+      </c>
+      <c r="E152" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F152" s="19" t="s">
         <v>234</v>
-      </c>
-      <c r="C152" s="90"/>
-      <c r="D152" s="90"/>
-      <c r="E152" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F152" s="24" t="s">
-        <v>235</v>
       </c>
       <c r="G152" s="92">
         <v>45901.0</v>
@@ -7040,335 +7177,345 @@
       <c r="K152" s="89"/>
     </row>
     <row r="153">
-      <c r="A153" s="6" t="s">
+      <c r="A153" s="23">
+        <v>18.0</v>
+      </c>
+      <c r="B153" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="C153" s="90"/>
+      <c r="D153" s="18">
+        <v>3.0</v>
+      </c>
+      <c r="E153" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F153" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="G153" s="92">
+        <v>45901.0</v>
+      </c>
+      <c r="H153" s="89"/>
+      <c r="I153" s="92">
+        <v>45901.0</v>
+      </c>
+      <c r="J153" s="89"/>
+      <c r="K153" s="89"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="23">
+        <v>18.0</v>
+      </c>
+      <c r="B154" s="18" t="s">
+        <v>237</v>
+      </c>
+      <c r="C154" s="90"/>
+      <c r="D154" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="E154" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F154" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="G154" s="92">
+        <v>45901.0</v>
+      </c>
+      <c r="H154" s="89"/>
+      <c r="I154" s="92">
+        <v>45901.0</v>
+      </c>
+      <c r="J154" s="89"/>
+      <c r="K154" s="89"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B153" s="4"/>
-      <c r="C153" s="4"/>
-      <c r="D153" s="4"/>
-      <c r="E153" s="4"/>
-      <c r="F153" s="5"/>
-      <c r="G153" s="6" t="s">
+      <c r="B155" s="4"/>
+      <c r="C155" s="4"/>
+      <c r="D155" s="4"/>
+      <c r="E155" s="4"/>
+      <c r="F155" s="5"/>
+      <c r="G155" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H153" s="5"/>
-      <c r="I153" s="3" t="s">
+      <c r="H155" s="5"/>
+      <c r="I155" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J153" s="5"/>
-      <c r="K153" s="5"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="6" t="s">
+      <c r="J155" s="5"/>
+      <c r="K155" s="5"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B154" s="4" t="s">
+      <c r="B156" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C154" s="4" t="s">
+      <c r="C156" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D154" s="4" t="s">
+      <c r="D156" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E154" s="4" t="s">
+      <c r="E156" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F154" s="7" t="s">
+      <c r="F156" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G154" s="6" t="s">
+      <c r="G156" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H154" s="5" t="s">
+      <c r="H156" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I154" s="6" t="s">
+      <c r="I156" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J154" s="5" t="s">
+      <c r="J156" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K154" s="8" t="s">
+      <c r="K156" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="73" t="s">
-        <v>236</v>
-      </c>
-      <c r="B155" s="74" t="s">
-        <v>237</v>
-      </c>
-      <c r="C155" s="123"/>
-      <c r="D155" s="123"/>
-      <c r="E155" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F155" s="75" t="s">
-        <v>238</v>
-      </c>
-      <c r="G155" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="H155" s="125"/>
-      <c r="I155" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="J155" s="125"/>
-      <c r="K155" s="125"/>
-    </row>
-    <row r="156">
-      <c r="A156" s="78">
-        <v>20.0</v>
-      </c>
-      <c r="B156" s="74" t="s">
+    <row r="157">
+      <c r="A157" s="73" t="s">
         <v>239</v>
       </c>
-      <c r="C156" s="123"/>
-      <c r="D156" s="123"/>
-      <c r="E156" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F156" s="75" t="s">
+      <c r="B157" s="74" t="s">
+        <v>135</v>
+      </c>
+      <c r="C157" s="122"/>
+      <c r="D157" s="74">
+        <v>9.0</v>
+      </c>
+      <c r="E157" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F157" s="75" t="s">
         <v>240</v>
       </c>
-      <c r="G156" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="H156" s="125"/>
-      <c r="I156" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="J156" s="125"/>
-      <c r="K156" s="125"/>
-    </row>
-    <row r="157">
-      <c r="A157" s="78">
-        <v>20.0</v>
-      </c>
-      <c r="B157" s="74" t="s">
+      <c r="G157" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H157" s="124"/>
+      <c r="I157" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J157" s="124"/>
+      <c r="K157" s="124"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="73"/>
+      <c r="B158" s="74" t="s">
         <v>241</v>
       </c>
-      <c r="C157" s="123"/>
-      <c r="D157" s="123"/>
-      <c r="E157" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F157" s="75" t="s">
+      <c r="C158" s="122"/>
+      <c r="D158" s="74">
+        <v>3.0</v>
+      </c>
+      <c r="E158" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F158" s="75" t="s">
         <v>242</v>
       </c>
-      <c r="G157" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="H157" s="125"/>
-      <c r="I157" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="J157" s="125"/>
-      <c r="K157" s="125"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="78">
-        <v>20.0</v>
-      </c>
-      <c r="B158" s="74" t="s">
-        <v>243</v>
-      </c>
-      <c r="C158" s="123"/>
-      <c r="D158" s="123"/>
-      <c r="E158" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F158" s="75" t="s">
-        <v>244</v>
-      </c>
-      <c r="G158" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="H158" s="125"/>
-      <c r="I158" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="J158" s="125"/>
-      <c r="K158" s="125"/>
+      <c r="G158" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H158" s="124"/>
+      <c r="I158" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J158" s="124"/>
+      <c r="K158" s="124"/>
     </row>
     <row r="159">
       <c r="A159" s="78">
         <v>20.0</v>
       </c>
       <c r="B159" s="74" t="s">
+        <v>243</v>
+      </c>
+      <c r="C159" s="122"/>
+      <c r="D159" s="74">
+        <v>5.0</v>
+      </c>
+      <c r="E159" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F159" s="75" t="s">
+        <v>244</v>
+      </c>
+      <c r="G159" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H159" s="124"/>
+      <c r="I159" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J159" s="124"/>
+      <c r="K159" s="124"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="78">
+        <v>20.0</v>
+      </c>
+      <c r="B160" s="74" t="s">
         <v>245</v>
       </c>
-      <c r="C159" s="123"/>
-      <c r="D159" s="123"/>
-      <c r="E159" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F159" s="126" t="s">
+      <c r="C160" s="122"/>
+      <c r="D160" s="74">
+        <v>4.0</v>
+      </c>
+      <c r="E160" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F160" s="75" t="s">
         <v>246</v>
       </c>
-      <c r="G159" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="H159" s="125"/>
-      <c r="I159" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="J159" s="125"/>
-      <c r="K159" s="125"/>
-    </row>
-    <row r="160">
-      <c r="A160" s="6" t="s">
+      <c r="G160" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H160" s="124"/>
+      <c r="I160" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J160" s="124"/>
+      <c r="K160" s="124"/>
+    </row>
+    <row r="161">
+      <c r="A161" s="78">
+        <v>20.0</v>
+      </c>
+      <c r="B161" s="74" t="s">
+        <v>247</v>
+      </c>
+      <c r="C161" s="122"/>
+      <c r="D161" s="74">
+        <v>4.0</v>
+      </c>
+      <c r="E161" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F161" s="75" t="s">
+        <v>248</v>
+      </c>
+      <c r="G161" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H161" s="124"/>
+      <c r="I161" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J161" s="124"/>
+      <c r="K161" s="124"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="78">
+        <v>20.0</v>
+      </c>
+      <c r="B162" s="74" t="s">
+        <v>249</v>
+      </c>
+      <c r="C162" s="122"/>
+      <c r="D162" s="74">
+        <v>3.0</v>
+      </c>
+      <c r="E162" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F162" s="125" t="s">
+        <v>250</v>
+      </c>
+      <c r="G162" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H162" s="124"/>
+      <c r="I162" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J162" s="124"/>
+      <c r="K162" s="124"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B160" s="4"/>
-      <c r="C160" s="4"/>
-      <c r="D160" s="4"/>
-      <c r="E160" s="4"/>
-      <c r="F160" s="5"/>
-      <c r="G160" s="6" t="s">
+      <c r="B163" s="4"/>
+      <c r="C163" s="4"/>
+      <c r="D163" s="4"/>
+      <c r="E163" s="4"/>
+      <c r="F163" s="5"/>
+      <c r="G163" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H160" s="5"/>
-      <c r="I160" s="3" t="s">
+      <c r="H163" s="5"/>
+      <c r="I163" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J160" s="5"/>
-      <c r="K160" s="5"/>
-    </row>
-    <row r="161">
-      <c r="A161" s="6" t="s">
+      <c r="J163" s="5"/>
+      <c r="K163" s="5"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B161" s="4" t="s">
+      <c r="B164" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C161" s="4" t="s">
+      <c r="C164" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D161" s="4" t="s">
+      <c r="D164" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E161" s="4" t="s">
+      <c r="E164" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F161" s="7" t="s">
+      <c r="F164" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G161" s="6" t="s">
+      <c r="G164" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H161" s="5" t="s">
+      <c r="H164" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I161" s="6" t="s">
+      <c r="I164" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J161" s="5" t="s">
+      <c r="J164" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K161" s="8" t="s">
+      <c r="K164" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="46" t="s">
-        <v>247</v>
-      </c>
-      <c r="B162" s="42" t="s">
+    <row r="165">
+      <c r="A165" s="46" t="s">
+        <v>251</v>
+      </c>
+      <c r="B165" s="42" t="s">
         <v>135</v>
-      </c>
-      <c r="C162" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="D162" s="105"/>
-      <c r="E162" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="F162" s="43" t="s">
-        <v>248</v>
-      </c>
-      <c r="G162" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="H162" s="107"/>
-      <c r="I162" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="J162" s="127"/>
-      <c r="K162" s="107"/>
-    </row>
-    <row r="163">
-      <c r="A163" s="128">
-        <v>22.0</v>
-      </c>
-      <c r="B163" s="42" t="s">
-        <v>249</v>
-      </c>
-      <c r="C163" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="D163" s="105"/>
-      <c r="E163" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="F163" s="43" t="s">
-        <v>250</v>
-      </c>
-      <c r="G163" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="H163" s="107"/>
-      <c r="I163" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="J163" s="127"/>
-      <c r="K163" s="107"/>
-    </row>
-    <row r="164">
-      <c r="A164" s="128">
-        <v>22.0</v>
-      </c>
-      <c r="B164" s="42" t="s">
-        <v>251</v>
-      </c>
-      <c r="C164" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="D164" s="105"/>
-      <c r="E164" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="F164" s="43" t="s">
-        <v>252</v>
-      </c>
-      <c r="G164" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="H164" s="107"/>
-      <c r="I164" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="J164" s="127"/>
-      <c r="K164" s="107"/>
-    </row>
-    <row r="165">
-      <c r="A165" s="128">
-        <v>22.0</v>
-      </c>
-      <c r="B165" s="42" t="s">
-        <v>253</v>
       </c>
       <c r="C165" s="42" t="s">
         <v>145</v>
       </c>
-      <c r="D165" s="105"/>
+      <c r="D165" s="42">
+        <v>9.0</v>
+      </c>
       <c r="E165" s="42" t="s">
         <v>146</v>
       </c>
       <c r="F165" s="43" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G165" s="106">
         <v>45901.0</v>
@@ -7377,25 +7524,27 @@
       <c r="I165" s="106">
         <v>45901.0</v>
       </c>
-      <c r="J165" s="127"/>
+      <c r="J165" s="126"/>
       <c r="K165" s="107"/>
     </row>
     <row r="166">
-      <c r="A166" s="128">
+      <c r="A166" s="127">
         <v>22.0</v>
       </c>
       <c r="B166" s="42" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C166" s="42" t="s">
         <v>145</v>
       </c>
-      <c r="D166" s="105"/>
+      <c r="D166" s="42">
+        <v>5.0</v>
+      </c>
       <c r="E166" s="42" t="s">
         <v>146</v>
       </c>
-      <c r="F166" s="110" t="s">
-        <v>256</v>
+      <c r="F166" s="43" t="s">
+        <v>254</v>
       </c>
       <c r="G166" s="106">
         <v>45901.0</v>
@@ -7404,531 +7553,563 @@
       <c r="I166" s="106">
         <v>45901.0</v>
       </c>
-      <c r="J166" s="127"/>
+      <c r="J166" s="126"/>
       <c r="K166" s="107"/>
     </row>
     <row r="167">
-      <c r="A167" s="6" t="s">
+      <c r="A167" s="127">
+        <v>22.0</v>
+      </c>
+      <c r="B167" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="C167" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="D167" s="42">
+        <v>6.0</v>
+      </c>
+      <c r="E167" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="F167" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="G167" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="H167" s="107"/>
+      <c r="I167" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="J167" s="126"/>
+      <c r="K167" s="107"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="127">
+        <v>22.0</v>
+      </c>
+      <c r="B168" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="C168" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="D168" s="42">
+        <v>3.0</v>
+      </c>
+      <c r="E168" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="F168" s="43" t="s">
+        <v>258</v>
+      </c>
+      <c r="G168" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="H168" s="107"/>
+      <c r="I168" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="J168" s="126"/>
+      <c r="K168" s="107"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="127">
+        <v>22.0</v>
+      </c>
+      <c r="B169" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="C169" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="D169" s="42">
+        <v>5.0</v>
+      </c>
+      <c r="E169" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="F169" s="43" t="s">
+        <v>260</v>
+      </c>
+      <c r="G169" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="H169" s="107"/>
+      <c r="I169" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="J169" s="126"/>
+      <c r="K169" s="107"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="127">
+        <v>22.0</v>
+      </c>
+      <c r="B170" s="42" t="s">
+        <v>261</v>
+      </c>
+      <c r="C170" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="D170" s="42">
+        <v>3.0</v>
+      </c>
+      <c r="E170" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="F170" s="110" t="s">
+        <v>262</v>
+      </c>
+      <c r="G170" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="H170" s="107"/>
+      <c r="I170" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="J170" s="126"/>
+      <c r="K170" s="107"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B167" s="4"/>
-      <c r="C167" s="4"/>
-      <c r="D167" s="4"/>
-      <c r="E167" s="4"/>
-      <c r="F167" s="5"/>
-      <c r="G167" s="6" t="s">
+      <c r="B171" s="4"/>
+      <c r="C171" s="4"/>
+      <c r="D171" s="4"/>
+      <c r="E171" s="4"/>
+      <c r="F171" s="5"/>
+      <c r="G171" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H167" s="5"/>
-      <c r="I167" s="3" t="s">
+      <c r="H171" s="5"/>
+      <c r="I171" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J167" s="5"/>
-      <c r="K167" s="5"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="6" t="s">
+      <c r="J171" s="5"/>
+      <c r="K171" s="5"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B168" s="4" t="s">
+      <c r="B172" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C168" s="4" t="s">
+      <c r="C172" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D168" s="4" t="s">
+      <c r="D172" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E168" s="4" t="s">
+      <c r="E172" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F168" s="7" t="s">
+      <c r="F172" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G168" s="6" t="s">
+      <c r="G172" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H168" s="5" t="s">
+      <c r="H172" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I168" s="6" t="s">
+      <c r="I172" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J168" s="5" t="s">
+      <c r="J172" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K168" s="8" t="s">
+      <c r="K172" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="129" t="s">
-        <v>257</v>
-      </c>
-      <c r="B169" s="130" t="s">
-        <v>258</v>
-      </c>
-      <c r="C169" s="130" t="s">
+    <row r="173">
+      <c r="A173" s="128" t="s">
+        <v>263</v>
+      </c>
+      <c r="B173" s="129" t="s">
+        <v>135</v>
+      </c>
+      <c r="C173" s="129" t="s">
         <v>145</v>
       </c>
-      <c r="D169" s="131"/>
-      <c r="E169" s="130" t="s">
+      <c r="D173" s="129">
+        <v>7.0</v>
+      </c>
+      <c r="E173" s="129" t="s">
         <v>146</v>
       </c>
-      <c r="F169" s="132" t="s">
-        <v>259</v>
-      </c>
-      <c r="G169" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="H169" s="134"/>
-      <c r="I169" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="J169" s="135">
+      <c r="F173" s="130" t="s">
+        <v>264</v>
+      </c>
+      <c r="G173" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="H173" s="132"/>
+      <c r="I173" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="J173" s="133">
         <v>45911.0</v>
       </c>
-      <c r="K169" s="134"/>
-    </row>
-    <row r="170">
-      <c r="A170" s="136">
+      <c r="K173" s="132"/>
+    </row>
+    <row r="174">
+      <c r="A174" s="128">
         <v>23.0</v>
       </c>
-      <c r="B170" s="130" t="s">
-        <v>260</v>
-      </c>
-      <c r="C170" s="130" t="s">
+      <c r="B174" s="129" t="s">
+        <v>265</v>
+      </c>
+      <c r="C174" s="129" t="s">
         <v>145</v>
       </c>
-      <c r="D170" s="131"/>
-      <c r="E170" s="130" t="s">
+      <c r="D174" s="129">
+        <v>3.0</v>
+      </c>
+      <c r="E174" s="129" t="s">
         <v>146</v>
       </c>
-      <c r="F170" s="132" t="s">
-        <v>261</v>
-      </c>
-      <c r="G170" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="H170" s="134"/>
-      <c r="I170" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="J170" s="135">
+      <c r="F174" s="130" t="s">
+        <v>266</v>
+      </c>
+      <c r="G174" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="H174" s="132"/>
+      <c r="I174" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="J174" s="133">
         <v>45911.0</v>
       </c>
-      <c r="K170" s="134"/>
-    </row>
-    <row r="171">
-      <c r="A171" s="136">
+      <c r="K174" s="132"/>
+    </row>
+    <row r="175">
+      <c r="A175" s="134">
         <v>23.0</v>
       </c>
-      <c r="B171" s="130" t="s">
-        <v>262</v>
-      </c>
-      <c r="C171" s="130" t="s">
+      <c r="B175" s="129" t="s">
+        <v>267</v>
+      </c>
+      <c r="C175" s="129" t="s">
         <v>145</v>
       </c>
-      <c r="D171" s="131"/>
-      <c r="E171" s="130" t="s">
+      <c r="D175" s="129">
+        <v>6.0</v>
+      </c>
+      <c r="E175" s="129" t="s">
         <v>146</v>
       </c>
-      <c r="F171" s="132" t="s">
-        <v>263</v>
-      </c>
-      <c r="G171" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="H171" s="134"/>
-      <c r="I171" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="J171" s="135">
+      <c r="F175" s="130" t="s">
+        <v>268</v>
+      </c>
+      <c r="G175" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="H175" s="132"/>
+      <c r="I175" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="J175" s="133">
         <v>45911.0</v>
       </c>
-      <c r="K171" s="134"/>
-    </row>
-    <row r="172">
-      <c r="A172" s="136">
+      <c r="K175" s="132"/>
+    </row>
+    <row r="176">
+      <c r="A176" s="134">
         <v>23.0</v>
       </c>
-      <c r="B172" s="130" t="s">
-        <v>264</v>
-      </c>
-      <c r="C172" s="130" t="s">
+      <c r="B176" s="129" t="s">
+        <v>269</v>
+      </c>
+      <c r="C176" s="129" t="s">
         <v>145</v>
       </c>
-      <c r="D172" s="131"/>
-      <c r="E172" s="130" t="s">
+      <c r="D176" s="129">
+        <v>3.0</v>
+      </c>
+      <c r="E176" s="129" t="s">
         <v>146</v>
       </c>
-      <c r="F172" s="132" t="s">
-        <v>265</v>
-      </c>
-      <c r="G172" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="H172" s="134"/>
-      <c r="I172" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="J172" s="135">
+      <c r="F176" s="130" t="s">
+        <v>270</v>
+      </c>
+      <c r="G176" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="H176" s="132"/>
+      <c r="I176" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="J176" s="133">
         <v>45911.0</v>
       </c>
-      <c r="K172" s="134"/>
-    </row>
-    <row r="173">
-      <c r="A173" s="136">
+      <c r="K176" s="132"/>
+    </row>
+    <row r="177">
+      <c r="A177" s="134">
         <v>23.0</v>
       </c>
-      <c r="B173" s="130" t="s">
-        <v>266</v>
-      </c>
-      <c r="C173" s="130" t="s">
+      <c r="B177" s="129" t="s">
+        <v>271</v>
+      </c>
+      <c r="C177" s="129" t="s">
         <v>145</v>
       </c>
-      <c r="D173" s="131"/>
-      <c r="E173" s="130" t="s">
+      <c r="D177" s="129">
+        <v>2.0</v>
+      </c>
+      <c r="E177" s="129" t="s">
         <v>146</v>
       </c>
-      <c r="F173" s="137" t="s">
-        <v>267</v>
-      </c>
-      <c r="G173" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="H173" s="134"/>
-      <c r="I173" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="J173" s="135">
+      <c r="F177" s="130" t="s">
+        <v>272</v>
+      </c>
+      <c r="G177" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="H177" s="132"/>
+      <c r="I177" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="J177" s="133">
         <v>45911.0</v>
       </c>
-      <c r="K173" s="134"/>
-    </row>
-    <row r="174">
-      <c r="A174" s="6" t="s">
+      <c r="K177" s="132"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="134">
+        <v>23.0</v>
+      </c>
+      <c r="B178" s="129" t="s">
+        <v>273</v>
+      </c>
+      <c r="C178" s="129" t="s">
+        <v>145</v>
+      </c>
+      <c r="D178" s="129">
+        <v>2.0</v>
+      </c>
+      <c r="E178" s="129" t="s">
+        <v>146</v>
+      </c>
+      <c r="F178" s="135" t="s">
+        <v>274</v>
+      </c>
+      <c r="G178" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="H178" s="132"/>
+      <c r="I178" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="J178" s="133">
+        <v>45911.0</v>
+      </c>
+      <c r="K178" s="132"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B174" s="4"/>
-      <c r="C174" s="4"/>
-      <c r="D174" s="4"/>
-      <c r="E174" s="4"/>
-      <c r="F174" s="5"/>
-      <c r="G174" s="6" t="s">
+      <c r="B179" s="4"/>
+      <c r="C179" s="4"/>
+      <c r="D179" s="4"/>
+      <c r="E179" s="4"/>
+      <c r="F179" s="5"/>
+      <c r="G179" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H174" s="5"/>
-      <c r="I174" s="3" t="s">
+      <c r="H179" s="5"/>
+      <c r="I179" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J174" s="5"/>
-      <c r="K174" s="5"/>
-    </row>
-    <row r="175">
-      <c r="A175" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B175" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C175" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D175" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E175" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F175" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G175" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H175" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I175" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J175" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="K175" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="65" t="s">
-        <v>268</v>
-      </c>
-      <c r="B176" s="66" t="s">
-        <v>269</v>
-      </c>
-      <c r="C176" s="66"/>
-      <c r="D176" s="119"/>
-      <c r="E176" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="F176" s="67" t="s">
-        <v>270</v>
-      </c>
-      <c r="G176" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H176" s="121"/>
-      <c r="I176" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="J176" s="138">
-        <v>45911.0</v>
-      </c>
-      <c r="K176" s="121"/>
-    </row>
-    <row r="177">
-      <c r="A177" s="71">
-        <v>24.0</v>
-      </c>
-      <c r="B177" s="66" t="s">
-        <v>271</v>
-      </c>
-      <c r="C177" s="66"/>
-      <c r="D177" s="119"/>
-      <c r="E177" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="F177" s="67" t="s">
-        <v>272</v>
-      </c>
-      <c r="G177" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H177" s="121"/>
-      <c r="I177" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="J177" s="138">
-        <v>45911.0</v>
-      </c>
-      <c r="K177" s="121"/>
-    </row>
-    <row r="178">
-      <c r="A178" s="71">
-        <v>24.0</v>
-      </c>
-      <c r="B178" s="66" t="s">
-        <v>273</v>
-      </c>
-      <c r="C178" s="66"/>
-      <c r="D178" s="119"/>
-      <c r="E178" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="F178" s="67" t="s">
-        <v>274</v>
-      </c>
-      <c r="G178" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H178" s="121"/>
-      <c r="I178" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="J178" s="138">
-        <v>45911.0</v>
-      </c>
-      <c r="K178" s="121"/>
-    </row>
-    <row r="179">
-      <c r="A179" s="71">
-        <v>24.0</v>
-      </c>
-      <c r="B179" s="66" t="s">
-        <v>275</v>
-      </c>
-      <c r="C179" s="66"/>
-      <c r="D179" s="119"/>
-      <c r="E179" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="F179" s="67" t="s">
-        <v>276</v>
-      </c>
-      <c r="G179" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H179" s="121"/>
-      <c r="I179" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="J179" s="138">
-        <v>45911.0</v>
-      </c>
-      <c r="K179" s="121"/>
+      <c r="J179" s="5"/>
+      <c r="K179" s="5"/>
     </row>
     <row r="180">
       <c r="A180" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B180" s="4"/>
-      <c r="C180" s="4"/>
-      <c r="D180" s="4"/>
-      <c r="E180" s="4"/>
-      <c r="F180" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="B180" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C180" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D180" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E180" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F180" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="G180" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H180" s="5"/>
-      <c r="I180" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J180" s="5"/>
-      <c r="K180" s="5"/>
+        <v>10</v>
+      </c>
+      <c r="H180" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I180" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J180" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K180" s="8" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="181">
-      <c r="A181" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B181" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C181" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D181" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E181" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F181" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G181" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H181" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I181" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J181" s="139" t="s">
-        <v>11</v>
-      </c>
-      <c r="K181" s="8" t="s">
-        <v>12</v>
-      </c>
+      <c r="A181" s="65" t="s">
+        <v>275</v>
+      </c>
+      <c r="B181" s="66" t="s">
+        <v>135</v>
+      </c>
+      <c r="C181" s="66"/>
+      <c r="D181" s="66">
+        <v>8.0</v>
+      </c>
+      <c r="E181" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F181" s="67" t="s">
+        <v>276</v>
+      </c>
+      <c r="G181" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H181" s="120"/>
+      <c r="I181" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="J181" s="136">
+        <v>45911.0</v>
+      </c>
+      <c r="K181" s="120"/>
     </row>
     <row r="182">
-      <c r="A182" s="11" t="s">
+      <c r="A182" s="65">
+        <v>24.0</v>
+      </c>
+      <c r="B182" s="66" t="s">
         <v>277</v>
       </c>
-      <c r="B182" s="10" t="s">
+      <c r="C182" s="66"/>
+      <c r="D182" s="66">
+        <v>3.0</v>
+      </c>
+      <c r="E182" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F182" s="67" t="s">
         <v>278</v>
       </c>
-      <c r="C182" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D182" s="84"/>
-      <c r="E182" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F182" s="12" t="s">
+      <c r="G182" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H182" s="120"/>
+      <c r="I182" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="J182" s="136">
+        <v>45911.0</v>
+      </c>
+      <c r="K182" s="120"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="71">
+        <v>24.0</v>
+      </c>
+      <c r="B183" s="66" t="s">
         <v>279</v>
       </c>
-      <c r="G182" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="H182" s="82"/>
-      <c r="I182" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="J182" s="140"/>
-      <c r="K182" s="82"/>
-    </row>
-    <row r="183">
-      <c r="A183" s="72">
-        <v>25.0</v>
-      </c>
-      <c r="B183" s="10" t="s">
+      <c r="C183" s="66"/>
+      <c r="D183" s="66">
+        <v>4.0</v>
+      </c>
+      <c r="E183" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F183" s="67" t="s">
         <v>280</v>
       </c>
-      <c r="C183" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D183" s="84"/>
-      <c r="E183" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F183" s="12" t="s">
+      <c r="G183" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H183" s="120"/>
+      <c r="I183" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="J183" s="136">
+        <v>45911.0</v>
+      </c>
+      <c r="K183" s="120"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="71">
+        <v>24.0</v>
+      </c>
+      <c r="B184" s="66" t="s">
         <v>281</v>
       </c>
-      <c r="G183" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="H183" s="82"/>
-      <c r="I183" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="J183" s="87"/>
-      <c r="K183" s="82"/>
-    </row>
-    <row r="184">
-      <c r="A184" s="72">
-        <v>25.0</v>
-      </c>
-      <c r="B184" s="10" t="s">
+      <c r="C184" s="66"/>
+      <c r="D184" s="66">
+        <v>2.0</v>
+      </c>
+      <c r="E184" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F184" s="67" t="s">
         <v>282</v>
       </c>
-      <c r="C184" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D184" s="84"/>
-      <c r="E184" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F184" s="12" t="s">
+      <c r="G184" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H184" s="120"/>
+      <c r="I184" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="J184" s="136">
+        <v>45911.0</v>
+      </c>
+      <c r="K184" s="120"/>
+    </row>
+    <row r="185">
+      <c r="A185" s="71">
+        <v>24.0</v>
+      </c>
+      <c r="B185" s="66" t="s">
         <v>283</v>
       </c>
-      <c r="G184" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="H184" s="82"/>
-      <c r="I184" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="J184" s="87"/>
-      <c r="K184" s="82"/>
-    </row>
-    <row r="185">
-      <c r="A185" s="72">
-        <v>25.0</v>
-      </c>
-      <c r="B185" s="10" t="s">
+      <c r="C185" s="66"/>
+      <c r="D185" s="66">
+        <v>3.0</v>
+      </c>
+      <c r="E185" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F185" s="67" t="s">
         <v>284</v>
       </c>
-      <c r="C185" s="11" t="s">
-        <v>145</v>
-      </c>
-      <c r="D185" s="84"/>
-      <c r="E185" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F185" s="12" t="s">
-        <v>285</v>
-      </c>
-      <c r="G185" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="H185" s="82"/>
-      <c r="I185" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="J185" s="87"/>
-      <c r="K185" s="82"/>
+      <c r="G185" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H185" s="120"/>
+      <c r="I185" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="J185" s="136">
+        <v>45911.0</v>
+      </c>
+      <c r="K185" s="120"/>
     </row>
     <row r="186">
       <c r="A186" s="6" t="s">
@@ -7977,7 +8158,7 @@
       <c r="I187" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J187" s="5" t="s">
+      <c r="J187" s="137" t="s">
         <v>11</v>
       </c>
       <c r="K187" s="8" t="s">
@@ -7985,139 +8166,149 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="28" t="s">
+      <c r="A188" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="B188" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="B188" s="29" t="s">
+      <c r="C188" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D188" s="11">
+        <v>6.0</v>
+      </c>
+      <c r="E188" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F188" s="12" t="s">
         <v>287</v>
       </c>
-      <c r="C188" s="29"/>
-      <c r="D188" s="96"/>
-      <c r="E188" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="F188" s="30" t="s">
+      <c r="G188" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="H188" s="82"/>
+      <c r="I188" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="J188" s="138"/>
+      <c r="K188" s="82"/>
+    </row>
+    <row r="189">
+      <c r="A189" s="11">
+        <v>25.0</v>
+      </c>
+      <c r="B189" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="G188" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="H188" s="95"/>
-      <c r="I188" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="J188" s="141">
-        <v>45908.0</v>
-      </c>
-      <c r="K188" s="95"/>
-    </row>
-    <row r="189">
-      <c r="A189" s="33">
-        <v>26.0</v>
-      </c>
-      <c r="B189" s="29" t="s">
+      <c r="C189" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D189" s="11">
+        <v>4.0</v>
+      </c>
+      <c r="E189" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F189" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="C189" s="29"/>
-      <c r="D189" s="96"/>
-      <c r="E189" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="F189" s="30" t="s">
+      <c r="G189" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="H189" s="82"/>
+      <c r="I189" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="J189" s="87"/>
+      <c r="K189" s="82"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="72">
+        <v>25.0</v>
+      </c>
+      <c r="B190" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="G189" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="H189" s="95"/>
-      <c r="I189" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="J189" s="141">
-        <v>45908.0</v>
-      </c>
-      <c r="K189" s="95"/>
-    </row>
-    <row r="190">
-      <c r="A190" s="33">
-        <v>26.0</v>
-      </c>
-      <c r="B190" s="29" t="s">
+      <c r="C190" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D190" s="11">
+        <v>3.0</v>
+      </c>
+      <c r="E190" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F190" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="C190" s="29"/>
-      <c r="D190" s="96"/>
-      <c r="E190" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="F190" s="30" t="s">
+      <c r="G190" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="H190" s="82"/>
+      <c r="I190" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="J190" s="87"/>
+      <c r="K190" s="82"/>
+    </row>
+    <row r="191">
+      <c r="A191" s="72">
+        <v>25.0</v>
+      </c>
+      <c r="B191" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="G190" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="H190" s="95"/>
-      <c r="I190" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="J190" s="141">
-        <v>45908.0</v>
-      </c>
-      <c r="K190" s="95"/>
-    </row>
-    <row r="191">
-      <c r="A191" s="33">
-        <v>26.0</v>
-      </c>
-      <c r="B191" s="29" t="s">
+      <c r="C191" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D191" s="11">
+        <v>3.0</v>
+      </c>
+      <c r="E191" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F191" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="C191" s="29"/>
-      <c r="D191" s="96"/>
-      <c r="E191" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="F191" s="30" t="s">
+      <c r="G191" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="H191" s="82"/>
+      <c r="I191" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="J191" s="87"/>
+      <c r="K191" s="82"/>
+    </row>
+    <row r="192">
+      <c r="A192" s="72">
+        <v>25.0</v>
+      </c>
+      <c r="B192" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="G191" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="H191" s="95"/>
-      <c r="I191" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="J191" s="141">
-        <v>45908.0</v>
-      </c>
-      <c r="K191" s="95"/>
-    </row>
-    <row r="192">
-      <c r="A192" s="33">
-        <v>26.0</v>
-      </c>
-      <c r="B192" s="29" t="s">
+      <c r="C192" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D192" s="11">
+        <v>2.0</v>
+      </c>
+      <c r="E192" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F192" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="C192" s="29"/>
-      <c r="D192" s="96"/>
-      <c r="E192" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="F192" s="142" t="s">
-        <v>296</v>
-      </c>
-      <c r="G192" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="H192" s="95"/>
-      <c r="I192" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="J192" s="141">
-        <v>45908.0</v>
-      </c>
-      <c r="K192" s="95"/>
+      <c r="G192" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="H192" s="82"/>
+      <c r="I192" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="J192" s="87"/>
+      <c r="K192" s="82"/>
     </row>
     <row r="193">
       <c r="A193" s="6" t="s">
@@ -8174,2776 +8365,3239 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="34" t="s">
+      <c r="A195" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="B195" s="29" t="s">
+        <v>135</v>
+      </c>
+      <c r="C195" s="29"/>
+      <c r="D195" s="29">
+        <v>9.0</v>
+      </c>
+      <c r="E195" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F195" s="30" t="s">
         <v>297</v>
       </c>
-      <c r="B195" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="C195" s="101"/>
-      <c r="D195" s="101"/>
-      <c r="E195" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="F195" s="36" t="s">
+      <c r="G195" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="H195" s="95"/>
+      <c r="I195" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="J195" s="139">
+        <v>45908.0</v>
+      </c>
+      <c r="K195" s="95"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="28">
+        <v>26.0</v>
+      </c>
+      <c r="B196" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="G195" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="H195" s="100"/>
-      <c r="I195" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="J195" s="100"/>
-      <c r="K195" s="100"/>
-    </row>
-    <row r="196">
-      <c r="A196" s="39">
-        <v>27.0</v>
-      </c>
-      <c r="B196" s="35" t="s">
+      <c r="C196" s="29"/>
+      <c r="D196" s="29">
+        <v>4.0</v>
+      </c>
+      <c r="E196" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F196" s="30" t="s">
         <v>299</v>
       </c>
-      <c r="C196" s="101"/>
-      <c r="D196" s="101"/>
-      <c r="E196" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="F196" s="36" t="s">
+      <c r="G196" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="H196" s="95"/>
+      <c r="I196" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="J196" s="139">
+        <v>45908.0</v>
+      </c>
+      <c r="K196" s="95"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="33">
+        <v>26.0</v>
+      </c>
+      <c r="B197" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="G196" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="H196" s="100"/>
-      <c r="I196" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="J196" s="100"/>
-      <c r="K196" s="100"/>
-    </row>
-    <row r="197">
-      <c r="A197" s="39">
-        <v>27.0</v>
-      </c>
-      <c r="B197" s="35" t="s">
+      <c r="C197" s="29"/>
+      <c r="D197" s="29">
+        <v>7.0</v>
+      </c>
+      <c r="E197" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F197" s="30" t="s">
         <v>301</v>
       </c>
-      <c r="C197" s="101"/>
-      <c r="D197" s="101"/>
-      <c r="E197" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="F197" s="36" t="s">
+      <c r="G197" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="H197" s="95"/>
+      <c r="I197" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="J197" s="139">
+        <v>45908.0</v>
+      </c>
+      <c r="K197" s="95"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="33">
+        <v>26.0</v>
+      </c>
+      <c r="B198" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="G197" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="H197" s="100"/>
-      <c r="I197" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="J197" s="100"/>
-      <c r="K197" s="100"/>
-    </row>
-    <row r="198">
-      <c r="A198" s="39">
-        <v>27.0</v>
-      </c>
-      <c r="B198" s="35" t="s">
+      <c r="C198" s="29"/>
+      <c r="D198" s="29">
+        <v>3.0</v>
+      </c>
+      <c r="E198" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F198" s="30" t="s">
         <v>303</v>
       </c>
-      <c r="C198" s="101"/>
-      <c r="D198" s="101"/>
-      <c r="E198" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="F198" s="36" t="s">
+      <c r="G198" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="H198" s="95"/>
+      <c r="I198" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="J198" s="139">
+        <v>45908.0</v>
+      </c>
+      <c r="K198" s="95"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="33">
+        <v>26.0</v>
+      </c>
+      <c r="B199" s="29" t="s">
         <v>304</v>
       </c>
-      <c r="G198" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="H198" s="100"/>
-      <c r="I198" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="J198" s="100"/>
-      <c r="K198" s="100"/>
-    </row>
-    <row r="199">
-      <c r="A199" s="39">
-        <v>27.0</v>
-      </c>
-      <c r="B199" s="35" t="s">
+      <c r="C199" s="29"/>
+      <c r="D199" s="29">
+        <v>3.0</v>
+      </c>
+      <c r="E199" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F199" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="C199" s="101"/>
-      <c r="D199" s="101"/>
-      <c r="E199" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="F199" s="40" t="s">
+      <c r="G199" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="H199" s="95"/>
+      <c r="I199" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="J199" s="139">
+        <v>45908.0</v>
+      </c>
+      <c r="K199" s="95"/>
+    </row>
+    <row r="200">
+      <c r="A200" s="33">
+        <v>26.0</v>
+      </c>
+      <c r="B200" s="29" t="s">
         <v>306</v>
       </c>
-      <c r="G199" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="H199" s="100"/>
-      <c r="I199" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="J199" s="100"/>
-      <c r="K199" s="100"/>
-    </row>
-    <row r="200">
-      <c r="A200" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B200" s="4"/>
-      <c r="C200" s="4"/>
-      <c r="D200" s="4"/>
-      <c r="E200" s="4"/>
-      <c r="F200" s="5"/>
-      <c r="G200" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H200" s="5"/>
-      <c r="I200" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J200" s="5"/>
-      <c r="K200" s="5"/>
+      <c r="C200" s="29"/>
+      <c r="D200" s="29">
+        <v>3.0</v>
+      </c>
+      <c r="E200" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F200" s="140" t="s">
+        <v>307</v>
+      </c>
+      <c r="G200" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="H200" s="95"/>
+      <c r="I200" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="J200" s="139">
+        <v>45908.0</v>
+      </c>
+      <c r="K200" s="95"/>
     </row>
     <row r="201">
       <c r="A201" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B201" s="4"/>
+      <c r="C201" s="4"/>
+      <c r="D201" s="4"/>
+      <c r="E201" s="4"/>
+      <c r="F201" s="5"/>
+      <c r="G201" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H201" s="5"/>
+      <c r="I201" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J201" s="5"/>
+      <c r="K201" s="5"/>
+    </row>
+    <row r="202">
+      <c r="A202" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B201" s="4" t="s">
+      <c r="B202" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C201" s="4" t="s">
+      <c r="C202" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D201" s="4" t="s">
+      <c r="D202" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E201" s="4" t="s">
+      <c r="E202" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F201" s="7" t="s">
+      <c r="F202" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G201" s="6" t="s">
+      <c r="G202" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H201" s="5" t="s">
+      <c r="H202" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I201" s="6" t="s">
+      <c r="I202" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J201" s="5" t="s">
+      <c r="J202" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K201" s="8" t="s">
+      <c r="K202" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="B202" s="42" t="s">
+    <row r="203">
+      <c r="A203" s="34" t="s">
         <v>308</v>
       </c>
-      <c r="C202" s="42" t="s">
+      <c r="B203" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="C203" s="101"/>
+      <c r="D203" s="35">
+        <v>6.0</v>
+      </c>
+      <c r="E203" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="F203" s="36" t="s">
+        <v>309</v>
+      </c>
+      <c r="G203" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="H203" s="100"/>
+      <c r="I203" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="J203" s="100"/>
+      <c r="K203" s="100"/>
+    </row>
+    <row r="204">
+      <c r="A204" s="39">
+        <v>27.0</v>
+      </c>
+      <c r="B204" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="C204" s="101"/>
+      <c r="D204" s="35">
+        <v>4.0</v>
+      </c>
+      <c r="E204" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="F204" s="36" t="s">
+        <v>311</v>
+      </c>
+      <c r="G204" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="H204" s="100"/>
+      <c r="I204" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="J204" s="100"/>
+      <c r="K204" s="100"/>
+    </row>
+    <row r="205">
+      <c r="A205" s="39">
+        <v>27.0</v>
+      </c>
+      <c r="B205" s="35" t="s">
+        <v>312</v>
+      </c>
+      <c r="C205" s="101"/>
+      <c r="D205" s="35">
+        <v>5.0</v>
+      </c>
+      <c r="E205" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="F205" s="36" t="s">
+        <v>313</v>
+      </c>
+      <c r="G205" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="H205" s="100"/>
+      <c r="I205" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="J205" s="100"/>
+      <c r="K205" s="100"/>
+    </row>
+    <row r="206">
+      <c r="A206" s="39">
+        <v>27.0</v>
+      </c>
+      <c r="B206" s="35" t="s">
+        <v>314</v>
+      </c>
+      <c r="C206" s="101"/>
+      <c r="D206" s="35">
+        <v>4.0</v>
+      </c>
+      <c r="E206" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="F206" s="36" t="s">
+        <v>315</v>
+      </c>
+      <c r="G206" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="H206" s="100"/>
+      <c r="I206" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="J206" s="100"/>
+      <c r="K206" s="100"/>
+    </row>
+    <row r="207">
+      <c r="A207" s="39">
+        <v>27.0</v>
+      </c>
+      <c r="B207" s="35" t="s">
+        <v>316</v>
+      </c>
+      <c r="C207" s="101"/>
+      <c r="D207" s="35">
+        <v>3.0</v>
+      </c>
+      <c r="E207" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="F207" s="40" t="s">
+        <v>317</v>
+      </c>
+      <c r="G207" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="H207" s="100"/>
+      <c r="I207" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="J207" s="100"/>
+      <c r="K207" s="100"/>
+    </row>
+    <row r="208">
+      <c r="A208" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B208" s="4"/>
+      <c r="C208" s="4"/>
+      <c r="D208" s="4"/>
+      <c r="E208" s="4"/>
+      <c r="F208" s="5"/>
+      <c r="G208" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H208" s="5"/>
+      <c r="I208" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J208" s="5"/>
+      <c r="K208" s="5"/>
+    </row>
+    <row r="209">
+      <c r="A209" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B209" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C209" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D209" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E209" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F209" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G209" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H209" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I209" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J209" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K209" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="46" t="s">
+        <v>318</v>
+      </c>
+      <c r="B210" s="42" t="s">
+        <v>319</v>
+      </c>
+      <c r="C210" s="42" t="s">
         <v>145</v>
       </c>
-      <c r="D202" s="105"/>
-      <c r="E202" s="42" t="s">
+      <c r="D210" s="42">
+        <v>7.0</v>
+      </c>
+      <c r="E210" s="42" t="s">
         <v>146</v>
       </c>
-      <c r="F202" s="43" t="s">
-        <v>309</v>
-      </c>
-      <c r="G202" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="H202" s="107"/>
-      <c r="I202" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="J202" s="45">
+      <c r="F210" s="43" t="s">
+        <v>320</v>
+      </c>
+      <c r="G210" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="H210" s="107"/>
+      <c r="I210" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="J210" s="45">
         <v>45914.0</v>
       </c>
-      <c r="K202" s="107"/>
-    </row>
-    <row r="203">
-      <c r="A203" s="128">
+      <c r="K210" s="107"/>
+    </row>
+    <row r="211">
+      <c r="A211" s="46"/>
+      <c r="B211" s="42" t="s">
+        <v>321</v>
+      </c>
+      <c r="C211" s="42" t="s">
+        <v>145</v>
+      </c>
+      <c r="D211" s="42">
+        <v>3.0</v>
+      </c>
+      <c r="E211" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="F211" s="43" t="s">
+        <v>322</v>
+      </c>
+      <c r="G211" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="H211" s="107"/>
+      <c r="I211" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="J211" s="45">
+        <v>45914.0</v>
+      </c>
+      <c r="K211" s="107"/>
+    </row>
+    <row r="212">
+      <c r="A212" s="127">
         <v>28.0</v>
       </c>
-      <c r="B203" s="42" t="s">
-        <v>310</v>
-      </c>
-      <c r="C203" s="42" t="s">
+      <c r="B212" s="42" t="s">
+        <v>323</v>
+      </c>
+      <c r="C212" s="42" t="s">
         <v>145</v>
       </c>
-      <c r="D203" s="105"/>
-      <c r="E203" s="42" t="s">
+      <c r="D212" s="42">
+        <v>5.0</v>
+      </c>
+      <c r="E212" s="42" t="s">
         <v>146</v>
       </c>
-      <c r="F203" s="43" t="s">
-        <v>311</v>
-      </c>
-      <c r="G203" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="H203" s="107"/>
-      <c r="I203" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="J203" s="45">
+      <c r="F212" s="43" t="s">
+        <v>324</v>
+      </c>
+      <c r="G212" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="H212" s="107"/>
+      <c r="I212" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="J212" s="45">
         <v>45915.0</v>
       </c>
-      <c r="K203" s="107"/>
-    </row>
-    <row r="204">
-      <c r="A204" s="128">
+      <c r="K212" s="107"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="127">
         <v>28.0</v>
       </c>
-      <c r="B204" s="42" t="s">
-        <v>312</v>
-      </c>
-      <c r="C204" s="42" t="s">
+      <c r="B213" s="42" t="s">
+        <v>325</v>
+      </c>
+      <c r="C213" s="42" t="s">
         <v>145</v>
       </c>
-      <c r="D204" s="105"/>
-      <c r="E204" s="42" t="s">
+      <c r="D213" s="42">
+        <v>3.0</v>
+      </c>
+      <c r="E213" s="42" t="s">
         <v>146</v>
       </c>
-      <c r="F204" s="43" t="s">
-        <v>313</v>
-      </c>
-      <c r="G204" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="H204" s="107"/>
-      <c r="I204" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="J204" s="45">
+      <c r="F213" s="43" t="s">
+        <v>326</v>
+      </c>
+      <c r="G213" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="H213" s="107"/>
+      <c r="I213" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="J213" s="45">
         <v>45916.0</v>
       </c>
-      <c r="K204" s="107"/>
-    </row>
-    <row r="205">
-      <c r="A205" s="128">
+      <c r="K213" s="107"/>
+    </row>
+    <row r="214">
+      <c r="A214" s="127">
         <v>28.0</v>
       </c>
-      <c r="B205" s="42" t="s">
-        <v>314</v>
-      </c>
-      <c r="C205" s="42" t="s">
+      <c r="B214" s="42" t="s">
+        <v>327</v>
+      </c>
+      <c r="C214" s="42" t="s">
         <v>145</v>
       </c>
-      <c r="D205" s="105"/>
-      <c r="E205" s="42" t="s">
+      <c r="D214" s="42">
+        <v>2.0</v>
+      </c>
+      <c r="E214" s="42" t="s">
         <v>146</v>
       </c>
-      <c r="F205" s="43" t="s">
-        <v>315</v>
-      </c>
-      <c r="G205" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="H205" s="107"/>
-      <c r="I205" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="J205" s="45">
+      <c r="F214" s="43" t="s">
+        <v>328</v>
+      </c>
+      <c r="G214" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="H214" s="107"/>
+      <c r="I214" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="J214" s="45">
         <v>45917.0</v>
       </c>
-      <c r="K205" s="107"/>
-    </row>
-    <row r="206">
-      <c r="A206" s="6" t="s">
+      <c r="K214" s="107"/>
+    </row>
+    <row r="215">
+      <c r="A215" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B206" s="4"/>
-      <c r="C206" s="4"/>
-      <c r="D206" s="4"/>
-      <c r="E206" s="4"/>
-      <c r="F206" s="5"/>
-      <c r="G206" s="6" t="s">
+      <c r="B215" s="4"/>
+      <c r="C215" s="4"/>
+      <c r="D215" s="4"/>
+      <c r="E215" s="4"/>
+      <c r="F215" s="5"/>
+      <c r="G215" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H206" s="5"/>
-      <c r="I206" s="3" t="s">
+      <c r="H215" s="5"/>
+      <c r="I215" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J206" s="5"/>
-      <c r="K206" s="5"/>
-    </row>
-    <row r="207">
-      <c r="A207" s="6" t="s">
+      <c r="J215" s="5"/>
+      <c r="K215" s="5"/>
+    </row>
+    <row r="216">
+      <c r="A216" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B207" s="4" t="s">
+      <c r="B216" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C207" s="4" t="s">
+      <c r="C216" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D207" s="4" t="s">
+      <c r="D216" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E207" s="4" t="s">
+      <c r="E216" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F207" s="7" t="s">
+      <c r="F216" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G207" s="6" t="s">
+      <c r="G216" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H207" s="5" t="s">
+      <c r="H216" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I207" s="6" t="s">
+      <c r="I216" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J207" s="5" t="s">
+      <c r="J216" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K207" s="8" t="s">
+      <c r="K216" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="53" t="s">
-        <v>316</v>
-      </c>
-      <c r="B208" s="49" t="s">
+    <row r="217">
+      <c r="A217" s="53" t="s">
+        <v>329</v>
+      </c>
+      <c r="B217" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="C208" s="111"/>
-      <c r="D208" s="111"/>
-      <c r="E208" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="F208" s="50" t="s">
-        <v>317</v>
-      </c>
-      <c r="G208" s="112">
-        <v>45901.0</v>
-      </c>
-      <c r="H208" s="113"/>
-      <c r="I208" s="112">
-        <v>45901.0</v>
-      </c>
-      <c r="J208" s="113"/>
-      <c r="K208" s="113"/>
-    </row>
-    <row r="209">
-      <c r="A209" s="143">
+      <c r="C217" s="111"/>
+      <c r="D217" s="49">
+        <v>9.0</v>
+      </c>
+      <c r="E217" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="F217" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="G217" s="112">
+        <v>45901.0</v>
+      </c>
+      <c r="H217" s="113"/>
+      <c r="I217" s="112">
+        <v>45901.0</v>
+      </c>
+      <c r="J217" s="113"/>
+      <c r="K217" s="113"/>
+    </row>
+    <row r="218">
+      <c r="A218" s="141">
         <v>29.0</v>
       </c>
-      <c r="B209" s="49" t="s">
-        <v>318</v>
-      </c>
-      <c r="C209" s="111"/>
-      <c r="D209" s="111"/>
-      <c r="E209" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="F209" s="50" t="s">
-        <v>319</v>
-      </c>
-      <c r="G209" s="112">
-        <v>45901.0</v>
-      </c>
-      <c r="H209" s="113"/>
-      <c r="I209" s="112">
-        <v>45901.0</v>
-      </c>
-      <c r="J209" s="113"/>
-      <c r="K209" s="113"/>
-    </row>
-    <row r="210">
-      <c r="A210" s="143">
+      <c r="B218" s="49" t="s">
+        <v>331</v>
+      </c>
+      <c r="C218" s="111"/>
+      <c r="D218" s="49">
+        <v>4.0</v>
+      </c>
+      <c r="E218" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="F218" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="G218" s="112">
+        <v>45901.0</v>
+      </c>
+      <c r="H218" s="113"/>
+      <c r="I218" s="112">
+        <v>45901.0</v>
+      </c>
+      <c r="J218" s="113"/>
+      <c r="K218" s="113"/>
+    </row>
+    <row r="219">
+      <c r="A219" s="141">
         <v>29.0</v>
       </c>
-      <c r="B210" s="49" t="s">
-        <v>320</v>
-      </c>
-      <c r="C210" s="111"/>
-      <c r="D210" s="111"/>
-      <c r="E210" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="F210" s="50" t="s">
-        <v>321</v>
-      </c>
-      <c r="G210" s="112">
-        <v>45901.0</v>
-      </c>
-      <c r="H210" s="113"/>
-      <c r="I210" s="112">
-        <v>45901.0</v>
-      </c>
-      <c r="J210" s="113"/>
-      <c r="K210" s="113"/>
-    </row>
-    <row r="211">
-      <c r="A211" s="143">
+      <c r="B219" s="49" t="s">
+        <v>333</v>
+      </c>
+      <c r="C219" s="111"/>
+      <c r="D219" s="49">
+        <v>8.0</v>
+      </c>
+      <c r="E219" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="F219" s="50" t="s">
+        <v>334</v>
+      </c>
+      <c r="G219" s="112">
+        <v>45901.0</v>
+      </c>
+      <c r="H219" s="113"/>
+      <c r="I219" s="112">
+        <v>45901.0</v>
+      </c>
+      <c r="J219" s="113"/>
+      <c r="K219" s="113"/>
+    </row>
+    <row r="220">
+      <c r="A220" s="141">
         <v>29.0</v>
       </c>
-      <c r="B211" s="49" t="s">
-        <v>322</v>
-      </c>
-      <c r="C211" s="111"/>
-      <c r="D211" s="111"/>
-      <c r="E211" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="F211" s="50" t="s">
-        <v>323</v>
-      </c>
-      <c r="G211" s="112">
-        <v>45901.0</v>
-      </c>
-      <c r="H211" s="113"/>
-      <c r="I211" s="112">
-        <v>45901.0</v>
-      </c>
-      <c r="J211" s="113"/>
-      <c r="K211" s="113"/>
-    </row>
-    <row r="212">
-      <c r="A212" s="143">
+      <c r="B220" s="49" t="s">
+        <v>335</v>
+      </c>
+      <c r="C220" s="111"/>
+      <c r="D220" s="49">
+        <v>5.0</v>
+      </c>
+      <c r="E220" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="F220" s="50" t="s">
+        <v>336</v>
+      </c>
+      <c r="G220" s="112">
+        <v>45901.0</v>
+      </c>
+      <c r="H220" s="113"/>
+      <c r="I220" s="112">
+        <v>45901.0</v>
+      </c>
+      <c r="J220" s="113"/>
+      <c r="K220" s="113"/>
+    </row>
+    <row r="221">
+      <c r="A221" s="141">
         <v>29.0</v>
       </c>
-      <c r="B212" s="49" t="s">
-        <v>324</v>
-      </c>
-      <c r="C212" s="111"/>
-      <c r="D212" s="111"/>
-      <c r="E212" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="F212" s="56" t="s">
-        <v>325</v>
-      </c>
-      <c r="G212" s="112">
-        <v>45901.0</v>
-      </c>
-      <c r="H212" s="113"/>
-      <c r="I212" s="112">
-        <v>45901.0</v>
-      </c>
-      <c r="J212" s="113"/>
-      <c r="K212" s="113"/>
-    </row>
-    <row r="213">
-      <c r="A213" s="6" t="s">
+      <c r="B221" s="49" t="s">
+        <v>337</v>
+      </c>
+      <c r="C221" s="111"/>
+      <c r="D221" s="49">
+        <v>4.0</v>
+      </c>
+      <c r="E221" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="F221" s="56" t="s">
+        <v>338</v>
+      </c>
+      <c r="G221" s="112">
+        <v>45901.0</v>
+      </c>
+      <c r="H221" s="113"/>
+      <c r="I221" s="112">
+        <v>45901.0</v>
+      </c>
+      <c r="J221" s="113"/>
+      <c r="K221" s="113"/>
+    </row>
+    <row r="222">
+      <c r="A222" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B213" s="4"/>
-      <c r="C213" s="4"/>
-      <c r="D213" s="4"/>
-      <c r="E213" s="4"/>
-      <c r="F213" s="5"/>
-      <c r="G213" s="6" t="s">
+      <c r="B222" s="4"/>
+      <c r="C222" s="4"/>
+      <c r="D222" s="4"/>
+      <c r="E222" s="4"/>
+      <c r="F222" s="5"/>
+      <c r="G222" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H213" s="5"/>
-      <c r="I213" s="3" t="s">
+      <c r="H222" s="5"/>
+      <c r="I222" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J213" s="5"/>
-      <c r="K213" s="5"/>
-    </row>
-    <row r="214">
-      <c r="A214" s="6" t="s">
+      <c r="J222" s="5"/>
+      <c r="K222" s="5"/>
+    </row>
+    <row r="223">
+      <c r="A223" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B214" s="4" t="s">
+      <c r="B223" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C214" s="4" t="s">
+      <c r="C223" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D214" s="4" t="s">
+      <c r="D223" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E214" s="4" t="s">
+      <c r="E223" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F214" s="7" t="s">
+      <c r="F223" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G214" s="6" t="s">
+      <c r="G223" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H214" s="5" t="s">
+      <c r="H223" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I214" s="6" t="s">
+      <c r="I223" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J214" s="5" t="s">
+      <c r="J223" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K214" s="8" t="s">
+      <c r="K223" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="215">
-      <c r="A215" s="57" t="s">
-        <v>326</v>
-      </c>
-      <c r="B215" s="58" t="s">
+    <row r="224">
+      <c r="A224" s="57" t="s">
+        <v>339</v>
+      </c>
+      <c r="B224" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="C215" s="116"/>
-      <c r="D215" s="116"/>
-      <c r="E215" s="58" t="s">
-        <v>65</v>
-      </c>
-      <c r="F215" s="59" t="s">
-        <v>327</v>
-      </c>
-      <c r="G215" s="117">
-        <v>45901.0</v>
-      </c>
-      <c r="H215" s="118"/>
-      <c r="I215" s="117">
-        <v>45901.0</v>
-      </c>
-      <c r="J215" s="118"/>
-      <c r="K215" s="118"/>
-    </row>
-    <row r="216">
-      <c r="A216" s="62">
+      <c r="C224" s="116"/>
+      <c r="D224" s="58">
+        <v>6.0</v>
+      </c>
+      <c r="E224" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="F224" s="59" t="s">
+        <v>340</v>
+      </c>
+      <c r="G224" s="117">
+        <v>45901.0</v>
+      </c>
+      <c r="H224" s="118"/>
+      <c r="I224" s="117">
+        <v>45901.0</v>
+      </c>
+      <c r="J224" s="118"/>
+      <c r="K224" s="118"/>
+    </row>
+    <row r="225">
+      <c r="A225" s="62">
         <v>30.0</v>
       </c>
-      <c r="B216" s="58" t="s">
-        <v>328</v>
-      </c>
-      <c r="C216" s="116"/>
-      <c r="D216" s="116"/>
-      <c r="E216" s="58" t="s">
-        <v>65</v>
-      </c>
-      <c r="F216" s="59" t="s">
-        <v>329</v>
-      </c>
-      <c r="G216" s="117">
-        <v>45901.0</v>
-      </c>
-      <c r="H216" s="118"/>
-      <c r="I216" s="117">
-        <v>45901.0</v>
-      </c>
-      <c r="J216" s="118"/>
-      <c r="K216" s="118"/>
-    </row>
-    <row r="217">
-      <c r="A217" s="62">
+      <c r="B225" s="58" t="s">
+        <v>341</v>
+      </c>
+      <c r="C225" s="116"/>
+      <c r="D225" s="58">
+        <v>3.0</v>
+      </c>
+      <c r="E225" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="F225" s="59" t="s">
+        <v>342</v>
+      </c>
+      <c r="G225" s="117">
+        <v>45901.0</v>
+      </c>
+      <c r="H225" s="118"/>
+      <c r="I225" s="117">
+        <v>45901.0</v>
+      </c>
+      <c r="J225" s="118"/>
+      <c r="K225" s="118"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="62">
         <v>30.0</v>
       </c>
-      <c r="B217" s="58" t="s">
+      <c r="B226" s="58" t="s">
+        <v>343</v>
+      </c>
+      <c r="C226" s="116"/>
+      <c r="D226" s="58">
+        <v>4.0</v>
+      </c>
+      <c r="E226" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="F226" s="59" t="s">
+        <v>344</v>
+      </c>
+      <c r="G226" s="117">
+        <v>45901.0</v>
+      </c>
+      <c r="H226" s="118"/>
+      <c r="I226" s="117">
+        <v>45901.0</v>
+      </c>
+      <c r="J226" s="118"/>
+      <c r="K226" s="118"/>
+    </row>
+    <row r="227">
+      <c r="A227" s="62">
+        <v>30.0</v>
+      </c>
+      <c r="B227" s="58" t="s">
+        <v>345</v>
+      </c>
+      <c r="C227" s="116"/>
+      <c r="D227" s="58">
+        <v>3.0</v>
+      </c>
+      <c r="E227" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="F227" s="59" t="s">
+        <v>346</v>
+      </c>
+      <c r="G227" s="117">
+        <v>45901.0</v>
+      </c>
+      <c r="H227" s="118"/>
+      <c r="I227" s="117">
+        <v>45901.0</v>
+      </c>
+      <c r="J227" s="118"/>
+      <c r="K227" s="118"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="62">
+        <v>30.0</v>
+      </c>
+      <c r="B228" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="C228" s="116"/>
+      <c r="D228" s="58">
+        <v>2.0</v>
+      </c>
+      <c r="E228" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="F228" s="64" t="s">
+        <v>348</v>
+      </c>
+      <c r="G228" s="117">
+        <v>45901.0</v>
+      </c>
+      <c r="H228" s="118"/>
+      <c r="I228" s="117">
+        <v>45901.0</v>
+      </c>
+      <c r="J228" s="118"/>
+      <c r="K228" s="118"/>
+    </row>
+    <row r="229">
+      <c r="A229" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B229" s="4"/>
+      <c r="C229" s="4"/>
+      <c r="D229" s="4"/>
+      <c r="E229" s="4"/>
+      <c r="F229" s="5"/>
+      <c r="G229" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H229" s="5"/>
+      <c r="I229" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J229" s="5"/>
+      <c r="K229" s="5"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B230" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C230" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D230" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E230" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F230" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G230" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H230" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I230" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J230" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K230" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="B231" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C231" s="90"/>
+      <c r="D231" s="18">
+        <v>8.0</v>
+      </c>
+      <c r="E231" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F231" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="C217" s="116"/>
-      <c r="D217" s="116"/>
-      <c r="E217" s="58" t="s">
-        <v>65</v>
-      </c>
-      <c r="F217" s="59" t="s">
+      <c r="G231" s="92">
+        <v>45901.0</v>
+      </c>
+      <c r="H231" s="89"/>
+      <c r="I231" s="92">
+        <v>45901.0</v>
+      </c>
+      <c r="J231" s="89"/>
+      <c r="K231" s="89"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="23">
+        <v>31.0</v>
+      </c>
+      <c r="B232" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="G217" s="117">
-        <v>45901.0</v>
-      </c>
-      <c r="H217" s="118"/>
-      <c r="I217" s="117">
-        <v>45901.0</v>
-      </c>
-      <c r="J217" s="118"/>
-      <c r="K217" s="118"/>
-    </row>
-    <row r="218">
-      <c r="A218" s="62">
-        <v>30.0</v>
-      </c>
-      <c r="B218" s="58" t="s">
+      <c r="C232" s="90"/>
+      <c r="D232" s="18">
+        <v>4.0</v>
+      </c>
+      <c r="E232" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F232" s="19" t="s">
         <v>332</v>
       </c>
-      <c r="C218" s="116"/>
-      <c r="D218" s="116"/>
-      <c r="E218" s="58" t="s">
-        <v>65</v>
-      </c>
-      <c r="F218" s="59" t="s">
+      <c r="G232" s="92">
+        <v>45901.0</v>
+      </c>
+      <c r="H232" s="89"/>
+      <c r="I232" s="92">
+        <v>45901.0</v>
+      </c>
+      <c r="J232" s="89"/>
+      <c r="K232" s="89"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="23">
+        <v>31.0</v>
+      </c>
+      <c r="B233" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="G218" s="117">
-        <v>45901.0</v>
-      </c>
-      <c r="H218" s="118"/>
-      <c r="I218" s="117">
-        <v>45901.0</v>
-      </c>
-      <c r="J218" s="118"/>
-      <c r="K218" s="118"/>
-    </row>
-    <row r="219">
-      <c r="A219" s="62">
-        <v>30.0</v>
-      </c>
-      <c r="B219" s="58" t="s">
+      <c r="C233" s="90"/>
+      <c r="D233" s="18">
+        <v>7.0</v>
+      </c>
+      <c r="E233" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F233" s="19" t="s">
         <v>334</v>
       </c>
-      <c r="C219" s="116"/>
-      <c r="D219" s="116"/>
-      <c r="E219" s="58" t="s">
-        <v>65</v>
-      </c>
-      <c r="F219" s="64" t="s">
+      <c r="G233" s="92">
+        <v>45901.0</v>
+      </c>
+      <c r="H233" s="89"/>
+      <c r="I233" s="92">
+        <v>45901.0</v>
+      </c>
+      <c r="J233" s="89"/>
+      <c r="K233" s="89"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="23">
+        <v>31.0</v>
+      </c>
+      <c r="B234" s="18" t="s">
         <v>335</v>
       </c>
-      <c r="G219" s="117">
-        <v>45901.0</v>
-      </c>
-      <c r="H219" s="118"/>
-      <c r="I219" s="117">
-        <v>45901.0</v>
-      </c>
-      <c r="J219" s="118"/>
-      <c r="K219" s="118"/>
-    </row>
-    <row r="220">
-      <c r="A220" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B220" s="4"/>
-      <c r="C220" s="4"/>
-      <c r="D220" s="4"/>
-      <c r="E220" s="4"/>
-      <c r="F220" s="5"/>
-      <c r="G220" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H220" s="5"/>
-      <c r="I220" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J220" s="5"/>
-      <c r="K220" s="5"/>
-    </row>
-    <row r="221">
-      <c r="A221" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B221" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C221" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D221" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E221" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F221" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G221" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H221" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I221" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J221" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="K221" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" s="17" t="s">
-        <v>336</v>
-      </c>
-      <c r="B222" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C222" s="90"/>
-      <c r="D222" s="90"/>
-      <c r="E222" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F222" s="19" t="s">
-        <v>317</v>
-      </c>
-      <c r="G222" s="92">
-        <v>45901.0</v>
-      </c>
-      <c r="H222" s="89"/>
-      <c r="I222" s="92">
-        <v>45901.0</v>
-      </c>
-      <c r="J222" s="89"/>
-      <c r="K222" s="89"/>
-    </row>
-    <row r="223">
-      <c r="A223" s="23">
+      <c r="C234" s="90"/>
+      <c r="D234" s="18">
+        <v>3.0</v>
+      </c>
+      <c r="E234" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F234" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="G234" s="92">
+        <v>45901.0</v>
+      </c>
+      <c r="H234" s="89"/>
+      <c r="I234" s="92">
+        <v>45901.0</v>
+      </c>
+      <c r="J234" s="89"/>
+      <c r="K234" s="89"/>
+    </row>
+    <row r="235">
+      <c r="A235" s="23">
         <v>31.0</v>
       </c>
-      <c r="B223" s="18" t="s">
-        <v>318</v>
-      </c>
-      <c r="C223" s="90"/>
-      <c r="D223" s="90"/>
-      <c r="E223" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F223" s="19" t="s">
-        <v>319</v>
-      </c>
-      <c r="G223" s="92">
-        <v>45901.0</v>
-      </c>
-      <c r="H223" s="89"/>
-      <c r="I223" s="92">
-        <v>45901.0</v>
-      </c>
-      <c r="J223" s="89"/>
-      <c r="K223" s="89"/>
-    </row>
-    <row r="224">
-      <c r="A224" s="23">
-        <v>31.0</v>
-      </c>
-      <c r="B224" s="18" t="s">
-        <v>320</v>
-      </c>
-      <c r="C224" s="90"/>
-      <c r="D224" s="90"/>
-      <c r="E224" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F224" s="19" t="s">
-        <v>321</v>
-      </c>
-      <c r="G224" s="92">
-        <v>45901.0</v>
-      </c>
-      <c r="H224" s="89"/>
-      <c r="I224" s="92">
-        <v>45901.0</v>
-      </c>
-      <c r="J224" s="89"/>
-      <c r="K224" s="89"/>
-    </row>
-    <row r="225">
-      <c r="A225" s="23">
-        <v>31.0</v>
-      </c>
-      <c r="B225" s="18" t="s">
-        <v>322</v>
-      </c>
-      <c r="C225" s="90"/>
-      <c r="D225" s="90"/>
-      <c r="E225" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F225" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="G225" s="92">
-        <v>45901.0</v>
-      </c>
-      <c r="H225" s="89"/>
-      <c r="I225" s="92">
-        <v>45901.0</v>
-      </c>
-      <c r="J225" s="89"/>
-      <c r="K225" s="89"/>
-    </row>
-    <row r="226">
-      <c r="A226" s="23">
-        <v>31.0</v>
-      </c>
-      <c r="B226" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="C226" s="90"/>
-      <c r="D226" s="90"/>
-      <c r="E226" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="F226" s="24" t="s">
-        <v>339</v>
-      </c>
-      <c r="G226" s="92">
-        <v>45901.0</v>
-      </c>
-      <c r="H226" s="89"/>
-      <c r="I226" s="92">
-        <v>45901.0</v>
-      </c>
-      <c r="J226" s="89"/>
-      <c r="K226" s="89"/>
-    </row>
-    <row r="227">
-      <c r="A227" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B227" s="4"/>
-      <c r="C227" s="4"/>
-      <c r="D227" s="4"/>
-      <c r="E227" s="4"/>
-      <c r="F227" s="5"/>
-      <c r="G227" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H227" s="5"/>
-      <c r="I227" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J227" s="5"/>
-      <c r="K227" s="5"/>
-    </row>
-    <row r="228">
-      <c r="A228" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B228" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C228" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D228" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E228" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F228" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G228" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H228" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="I228" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="J228" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="K228" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" s="73" t="s">
-        <v>340</v>
-      </c>
-      <c r="B229" s="74" t="s">
-        <v>135</v>
-      </c>
-      <c r="C229" s="123"/>
-      <c r="D229" s="123"/>
-      <c r="E229" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F229" s="75" t="s">
-        <v>341</v>
-      </c>
-      <c r="G229" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="H229" s="125"/>
-      <c r="I229" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="J229" s="125"/>
-      <c r="K229" s="125"/>
-    </row>
-    <row r="230">
-      <c r="A230" s="78">
-        <v>33.0</v>
-      </c>
-      <c r="B230" s="74" t="s">
-        <v>342</v>
-      </c>
-      <c r="C230" s="123"/>
-      <c r="D230" s="123"/>
-      <c r="E230" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F230" s="75" t="s">
-        <v>343</v>
-      </c>
-      <c r="G230" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="H230" s="125"/>
-      <c r="I230" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="J230" s="125"/>
-      <c r="K230" s="125"/>
-    </row>
-    <row r="231">
-      <c r="A231" s="78">
-        <v>33.0</v>
-      </c>
-      <c r="B231" s="74" t="s">
-        <v>344</v>
-      </c>
-      <c r="C231" s="123"/>
-      <c r="D231" s="123"/>
-      <c r="E231" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F231" s="75" t="s">
-        <v>345</v>
-      </c>
-      <c r="G231" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="H231" s="125"/>
-      <c r="I231" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="J231" s="125"/>
-      <c r="K231" s="125"/>
-    </row>
-    <row r="232">
-      <c r="A232" s="78">
-        <v>33.0</v>
-      </c>
-      <c r="B232" s="74" t="s">
-        <v>346</v>
-      </c>
-      <c r="C232" s="123"/>
-      <c r="D232" s="123"/>
-      <c r="E232" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F232" s="75" t="s">
-        <v>347</v>
-      </c>
-      <c r="G232" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="H232" s="125"/>
-      <c r="I232" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="J232" s="125"/>
-      <c r="K232" s="125"/>
-    </row>
-    <row r="233">
-      <c r="A233" s="78">
-        <v>33.0</v>
-      </c>
-      <c r="B233" s="74" t="s">
-        <v>348</v>
-      </c>
-      <c r="C233" s="123"/>
-      <c r="D233" s="123"/>
-      <c r="E233" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F233" s="75" t="s">
-        <v>349</v>
-      </c>
-      <c r="G233" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="H233" s="125"/>
-      <c r="I233" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="J233" s="125"/>
-      <c r="K233" s="125"/>
-    </row>
-    <row r="234">
-      <c r="A234" s="78">
-        <v>33.0</v>
-      </c>
-      <c r="B234" s="74" t="s">
-        <v>350</v>
-      </c>
-      <c r="C234" s="123"/>
-      <c r="D234" s="123"/>
-      <c r="E234" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F234" s="126" t="s">
+      <c r="B235" s="18" t="s">
         <v>351</v>
       </c>
-      <c r="G234" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="H234" s="125"/>
-      <c r="I234" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="J234" s="125"/>
-      <c r="K234" s="125"/>
-    </row>
-    <row r="235">
-      <c r="A235" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B235" s="4"/>
-      <c r="C235" s="4"/>
-      <c r="D235" s="4"/>
-      <c r="E235" s="4"/>
-      <c r="F235" s="5"/>
-      <c r="G235" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H235" s="5"/>
-      <c r="I235" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J235" s="5"/>
-      <c r="K235" s="5"/>
+      <c r="C235" s="90"/>
+      <c r="D235" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="E235" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="F235" s="24" t="s">
+        <v>352</v>
+      </c>
+      <c r="G235" s="92">
+        <v>45901.0</v>
+      </c>
+      <c r="H235" s="89"/>
+      <c r="I235" s="92">
+        <v>45901.0</v>
+      </c>
+      <c r="J235" s="89"/>
+      <c r="K235" s="89"/>
     </row>
     <row r="236">
       <c r="A236" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B236" s="4"/>
+      <c r="C236" s="4"/>
+      <c r="D236" s="4"/>
+      <c r="E236" s="4"/>
+      <c r="F236" s="5"/>
+      <c r="G236" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H236" s="5"/>
+      <c r="I236" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J236" s="5"/>
+      <c r="K236" s="5"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B236" s="4" t="s">
+      <c r="B237" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C236" s="4" t="s">
+      <c r="C237" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D236" s="4" t="s">
+      <c r="D237" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E236" s="4" t="s">
+      <c r="E237" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F236" s="7" t="s">
+      <c r="F237" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G236" s="6" t="s">
+      <c r="G237" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H236" s="5" t="s">
+      <c r="H237" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I236" s="6" t="s">
+      <c r="I237" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J236" s="5" t="s">
+      <c r="J237" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K236" s="8" t="s">
+      <c r="K237" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="237">
-      <c r="A237" s="129" t="s">
-        <v>352</v>
-      </c>
-      <c r="B237" s="130" t="s">
+    <row r="238">
+      <c r="A238" s="73" t="s">
+        <v>353</v>
+      </c>
+      <c r="B238" s="74" t="s">
         <v>135</v>
       </c>
-      <c r="C237" s="131"/>
-      <c r="D237" s="131"/>
-      <c r="E237" s="130" t="s">
-        <v>65</v>
-      </c>
-      <c r="F237" s="132" t="s">
-        <v>353</v>
-      </c>
-      <c r="G237" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="H237" s="134"/>
-      <c r="I237" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="J237" s="134"/>
-      <c r="K237" s="134"/>
-    </row>
-    <row r="238">
-      <c r="A238" s="136">
-        <v>36.0</v>
-      </c>
-      <c r="B238" s="130" t="s">
+      <c r="C238" s="122"/>
+      <c r="D238" s="74">
+        <v>5.0</v>
+      </c>
+      <c r="E238" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F238" s="75" t="s">
         <v>354</v>
       </c>
-      <c r="C238" s="131"/>
-      <c r="D238" s="131"/>
-      <c r="E238" s="130" t="s">
-        <v>65</v>
-      </c>
-      <c r="F238" s="132" t="s">
+      <c r="G238" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H238" s="124"/>
+      <c r="I238" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J238" s="124"/>
+      <c r="K238" s="124"/>
+    </row>
+    <row r="239">
+      <c r="A239" s="78">
+        <v>33.0</v>
+      </c>
+      <c r="B239" s="74" t="s">
         <v>355</v>
       </c>
-      <c r="G238" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="H238" s="134"/>
-      <c r="I238" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="J238" s="134"/>
-      <c r="K238" s="134"/>
-    </row>
-    <row r="239">
-      <c r="A239" s="136">
-        <v>36.0</v>
-      </c>
-      <c r="B239" s="130" t="s">
+      <c r="C239" s="122"/>
+      <c r="D239" s="74">
+        <v>3.0</v>
+      </c>
+      <c r="E239" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F239" s="75" t="s">
         <v>356</v>
       </c>
-      <c r="C239" s="131"/>
-      <c r="D239" s="131"/>
-      <c r="E239" s="130" t="s">
-        <v>65</v>
-      </c>
-      <c r="F239" s="132" t="s">
+      <c r="G239" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H239" s="124"/>
+      <c r="I239" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J239" s="124"/>
+      <c r="K239" s="124"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="78">
+        <v>33.0</v>
+      </c>
+      <c r="B240" s="74" t="s">
         <v>357</v>
       </c>
-      <c r="G239" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="H239" s="134"/>
-      <c r="I239" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="J239" s="134"/>
-      <c r="K239" s="134"/>
-    </row>
-    <row r="240">
-      <c r="A240" s="136">
-        <v>36.0</v>
-      </c>
-      <c r="B240" s="130" t="s">
+      <c r="C240" s="122"/>
+      <c r="D240" s="74">
+        <v>3.0</v>
+      </c>
+      <c r="E240" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F240" s="75" t="s">
         <v>358</v>
       </c>
-      <c r="C240" s="131"/>
-      <c r="D240" s="131"/>
-      <c r="E240" s="130" t="s">
-        <v>65</v>
-      </c>
-      <c r="F240" s="132" t="s">
+      <c r="G240" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H240" s="124"/>
+      <c r="I240" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J240" s="124"/>
+      <c r="K240" s="124"/>
+    </row>
+    <row r="241">
+      <c r="A241" s="78">
+        <v>33.0</v>
+      </c>
+      <c r="B241" s="74" t="s">
         <v>359</v>
       </c>
-      <c r="G240" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="H240" s="134"/>
-      <c r="I240" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="J240" s="134"/>
-      <c r="K240" s="134"/>
-    </row>
-    <row r="241">
-      <c r="A241" s="136">
-        <v>36.0</v>
-      </c>
-      <c r="B241" s="130" t="s">
+      <c r="C241" s="122"/>
+      <c r="D241" s="74">
+        <v>6.0</v>
+      </c>
+      <c r="E241" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F241" s="75" t="s">
         <v>360</v>
       </c>
-      <c r="C241" s="131"/>
-      <c r="D241" s="131"/>
-      <c r="E241" s="130" t="s">
-        <v>65</v>
-      </c>
-      <c r="F241" s="132" t="s">
+      <c r="G241" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H241" s="124"/>
+      <c r="I241" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J241" s="124"/>
+      <c r="K241" s="124"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="78">
+        <v>33.0</v>
+      </c>
+      <c r="B242" s="74" t="s">
         <v>361</v>
       </c>
-      <c r="G241" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="H241" s="134"/>
-      <c r="I241" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="J241" s="134"/>
-      <c r="K241" s="134"/>
-    </row>
-    <row r="242">
-      <c r="A242" s="136">
-        <v>36.0</v>
-      </c>
-      <c r="B242" s="130" t="s">
+      <c r="C242" s="122"/>
+      <c r="D242" s="74">
+        <v>5.0</v>
+      </c>
+      <c r="E242" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F242" s="75" t="s">
         <v>362</v>
       </c>
-      <c r="C242" s="131"/>
-      <c r="D242" s="131"/>
-      <c r="E242" s="130" t="s">
-        <v>65</v>
-      </c>
-      <c r="F242" s="137" t="s">
+      <c r="G242" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H242" s="124"/>
+      <c r="I242" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J242" s="124"/>
+      <c r="K242" s="124"/>
+    </row>
+    <row r="243">
+      <c r="A243" s="78">
+        <v>33.0</v>
+      </c>
+      <c r="B243" s="74" t="s">
         <v>363</v>
       </c>
-      <c r="G242" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="H242" s="134"/>
-      <c r="I242" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="J242" s="134"/>
-      <c r="K242" s="134"/>
-    </row>
-    <row r="243">
-      <c r="A243" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B243" s="4"/>
-      <c r="C243" s="4"/>
-      <c r="D243" s="4"/>
-      <c r="E243" s="4"/>
-      <c r="F243" s="5"/>
-      <c r="G243" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="H243" s="5"/>
-      <c r="I243" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J243" s="5"/>
-      <c r="K243" s="5"/>
+      <c r="C243" s="122"/>
+      <c r="D243" s="74">
+        <v>3.0</v>
+      </c>
+      <c r="E243" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F243" s="125" t="s">
+        <v>364</v>
+      </c>
+      <c r="G243" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H243" s="124"/>
+      <c r="I243" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J243" s="124"/>
+      <c r="K243" s="124"/>
     </row>
     <row r="244">
       <c r="A244" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B244" s="4"/>
+      <c r="C244" s="4"/>
+      <c r="D244" s="4"/>
+      <c r="E244" s="4"/>
+      <c r="F244" s="5"/>
+      <c r="G244" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H244" s="5"/>
+      <c r="I244" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J244" s="5"/>
+      <c r="K244" s="5"/>
+    </row>
+    <row r="245">
+      <c r="A245" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B244" s="4" t="s">
+      <c r="B245" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C244" s="4" t="s">
+      <c r="C245" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D244" s="4" t="s">
+      <c r="D245" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E244" s="4" t="s">
+      <c r="E245" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F244" s="7" t="s">
+      <c r="F245" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G244" s="6" t="s">
+      <c r="G245" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H244" s="5" t="s">
+      <c r="H245" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I244" s="6" t="s">
+      <c r="I245" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J244" s="5" t="s">
+      <c r="J245" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K244" s="8" t="s">
+      <c r="K245" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="65" t="s">
-        <v>364</v>
-      </c>
-      <c r="B245" s="66" t="s">
+    <row r="246">
+      <c r="A246" s="128" t="s">
+        <v>365</v>
+      </c>
+      <c r="B246" s="129" t="s">
         <v>135</v>
       </c>
-      <c r="C245" s="119"/>
-      <c r="D245" s="119"/>
-      <c r="E245" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="F245" s="67" t="s">
-        <v>365</v>
-      </c>
-      <c r="G245" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H245" s="121"/>
-      <c r="I245" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="J245" s="121"/>
-      <c r="K245" s="121"/>
-    </row>
-    <row r="246">
-      <c r="A246" s="71">
+      <c r="C246" s="142"/>
+      <c r="D246" s="129">
+        <v>6.0</v>
+      </c>
+      <c r="E246" s="129" t="s">
+        <v>65</v>
+      </c>
+      <c r="F246" s="130" t="s">
+        <v>366</v>
+      </c>
+      <c r="G246" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="H246" s="132"/>
+      <c r="I246" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="J246" s="132"/>
+      <c r="K246" s="132"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="134">
+        <v>36.0</v>
+      </c>
+      <c r="B247" s="129" t="s">
+        <v>367</v>
+      </c>
+      <c r="C247" s="142"/>
+      <c r="D247" s="129">
+        <v>3.0</v>
+      </c>
+      <c r="E247" s="129" t="s">
+        <v>65</v>
+      </c>
+      <c r="F247" s="130" t="s">
+        <v>368</v>
+      </c>
+      <c r="G247" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="H247" s="132"/>
+      <c r="I247" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="J247" s="132"/>
+      <c r="K247" s="132"/>
+    </row>
+    <row r="248">
+      <c r="A248" s="134">
+        <v>36.0</v>
+      </c>
+      <c r="B248" s="129" t="s">
+        <v>369</v>
+      </c>
+      <c r="C248" s="142"/>
+      <c r="D248" s="129">
+        <v>5.0</v>
+      </c>
+      <c r="E248" s="129" t="s">
+        <v>65</v>
+      </c>
+      <c r="F248" s="130" t="s">
+        <v>370</v>
+      </c>
+      <c r="G248" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="H248" s="132"/>
+      <c r="I248" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="J248" s="132"/>
+      <c r="K248" s="132"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="134">
+        <v>36.0</v>
+      </c>
+      <c r="B249" s="129" t="s">
+        <v>371</v>
+      </c>
+      <c r="C249" s="142"/>
+      <c r="D249" s="129">
+        <v>2.0</v>
+      </c>
+      <c r="E249" s="129" t="s">
+        <v>65</v>
+      </c>
+      <c r="F249" s="130" t="s">
+        <v>372</v>
+      </c>
+      <c r="G249" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="H249" s="132"/>
+      <c r="I249" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="J249" s="132"/>
+      <c r="K249" s="132"/>
+    </row>
+    <row r="250">
+      <c r="A250" s="134">
+        <v>36.0</v>
+      </c>
+      <c r="B250" s="129" t="s">
+        <v>373</v>
+      </c>
+      <c r="C250" s="142"/>
+      <c r="D250" s="129">
+        <v>2.0</v>
+      </c>
+      <c r="E250" s="129" t="s">
+        <v>65</v>
+      </c>
+      <c r="F250" s="130" t="s">
+        <v>374</v>
+      </c>
+      <c r="G250" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="H250" s="132"/>
+      <c r="I250" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="J250" s="132"/>
+      <c r="K250" s="132"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="134">
+        <v>36.0</v>
+      </c>
+      <c r="B251" s="129" t="s">
+        <v>375</v>
+      </c>
+      <c r="C251" s="142"/>
+      <c r="D251" s="129">
+        <v>3.0</v>
+      </c>
+      <c r="E251" s="129" t="s">
+        <v>65</v>
+      </c>
+      <c r="F251" s="135" t="s">
+        <v>376</v>
+      </c>
+      <c r="G251" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="H251" s="132"/>
+      <c r="I251" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="J251" s="132"/>
+      <c r="K251" s="132"/>
+    </row>
+    <row r="252">
+      <c r="A252" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B252" s="4"/>
+      <c r="C252" s="4"/>
+      <c r="D252" s="4"/>
+      <c r="E252" s="4"/>
+      <c r="F252" s="5"/>
+      <c r="G252" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="H252" s="5"/>
+      <c r="I252" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J252" s="5"/>
+      <c r="K252" s="5"/>
+    </row>
+    <row r="253">
+      <c r="A253" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D253" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E253" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F253" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G253" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="H253" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I253" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J253" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K253" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="65" t="s">
+        <v>377</v>
+      </c>
+      <c r="B254" s="66" t="s">
+        <v>135</v>
+      </c>
+      <c r="C254" s="143"/>
+      <c r="D254" s="66">
+        <v>6.0</v>
+      </c>
+      <c r="E254" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F254" s="67" t="s">
+        <v>378</v>
+      </c>
+      <c r="G254" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H254" s="120"/>
+      <c r="I254" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="J254" s="120"/>
+      <c r="K254" s="120"/>
+    </row>
+    <row r="255">
+      <c r="A255" s="71">
         <v>37.0</v>
       </c>
-      <c r="B246" s="66" t="s">
-        <v>366</v>
-      </c>
-      <c r="C246" s="119"/>
-      <c r="D246" s="119"/>
-      <c r="E246" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="F246" s="67" t="s">
-        <v>367</v>
-      </c>
-      <c r="G246" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H246" s="121"/>
-      <c r="I246" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="J246" s="121"/>
-      <c r="K246" s="121"/>
-    </row>
-    <row r="247">
-      <c r="A247" s="71">
+      <c r="B255" s="66" t="s">
+        <v>379</v>
+      </c>
+      <c r="C255" s="143"/>
+      <c r="D255" s="66">
+        <v>2.0</v>
+      </c>
+      <c r="E255" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F255" s="67" t="s">
+        <v>380</v>
+      </c>
+      <c r="G255" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H255" s="120"/>
+      <c r="I255" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="J255" s="120"/>
+      <c r="K255" s="120"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="71">
         <v>37.0</v>
       </c>
-      <c r="B247" s="66" t="s">
-        <v>368</v>
-      </c>
-      <c r="C247" s="119"/>
-      <c r="D247" s="119"/>
-      <c r="E247" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="F247" s="67" t="s">
-        <v>369</v>
-      </c>
-      <c r="G247" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H247" s="121"/>
-      <c r="I247" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="J247" s="121"/>
-      <c r="K247" s="121"/>
-    </row>
-    <row r="248">
-      <c r="A248" s="71">
+      <c r="B256" s="66" t="s">
+        <v>381</v>
+      </c>
+      <c r="C256" s="143"/>
+      <c r="D256" s="66">
+        <v>3.0</v>
+      </c>
+      <c r="E256" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F256" s="67" t="s">
+        <v>382</v>
+      </c>
+      <c r="G256" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H256" s="120"/>
+      <c r="I256" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="J256" s="120"/>
+      <c r="K256" s="120"/>
+    </row>
+    <row r="257">
+      <c r="A257" s="71">
         <v>37.0</v>
       </c>
-      <c r="B248" s="66" t="s">
-        <v>370</v>
-      </c>
-      <c r="C248" s="119"/>
-      <c r="D248" s="119"/>
-      <c r="E248" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="F248" s="67" t="s">
-        <v>371</v>
-      </c>
-      <c r="G248" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H248" s="121"/>
-      <c r="I248" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="J248" s="121"/>
-      <c r="K248" s="121"/>
-    </row>
-    <row r="249">
-      <c r="A249" s="71">
+      <c r="B257" s="66" t="s">
+        <v>383</v>
+      </c>
+      <c r="C257" s="143"/>
+      <c r="D257" s="66">
+        <v>3.0</v>
+      </c>
+      <c r="E257" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F257" s="67" t="s">
+        <v>384</v>
+      </c>
+      <c r="G257" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H257" s="120"/>
+      <c r="I257" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="J257" s="120"/>
+      <c r="K257" s="120"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="71">
         <v>37.0</v>
       </c>
-      <c r="B249" s="66" t="s">
-        <v>372</v>
-      </c>
-      <c r="C249" s="119"/>
-      <c r="D249" s="119"/>
-      <c r="E249" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="F249" s="122" t="s">
-        <v>373</v>
-      </c>
-      <c r="G249" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H249" s="121"/>
-      <c r="I249" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="J249" s="121"/>
-      <c r="K249" s="121"/>
-    </row>
-    <row r="250">
-      <c r="A250" s="6" t="s">
+      <c r="B258" s="66" t="s">
+        <v>385</v>
+      </c>
+      <c r="C258" s="143"/>
+      <c r="D258" s="66">
+        <v>4.0</v>
+      </c>
+      <c r="E258" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F258" s="121" t="s">
+        <v>386</v>
+      </c>
+      <c r="G258" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H258" s="120"/>
+      <c r="I258" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="J258" s="120"/>
+      <c r="K258" s="120"/>
+    </row>
+    <row r="259">
+      <c r="A259" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B250" s="4"/>
-      <c r="C250" s="4"/>
-      <c r="D250" s="4"/>
-      <c r="E250" s="4"/>
-      <c r="F250" s="5"/>
-      <c r="G250" s="6" t="s">
+      <c r="B259" s="4"/>
+      <c r="C259" s="4"/>
+      <c r="D259" s="4"/>
+      <c r="E259" s="4"/>
+      <c r="F259" s="5"/>
+      <c r="G259" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H250" s="5"/>
-      <c r="I250" s="3" t="s">
+      <c r="H259" s="5"/>
+      <c r="I259" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J250" s="5"/>
-      <c r="K250" s="5"/>
-    </row>
-    <row r="251">
-      <c r="A251" s="6" t="s">
+      <c r="J259" s="5"/>
+      <c r="K259" s="5"/>
+    </row>
+    <row r="260">
+      <c r="A260" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B251" s="4" t="s">
+      <c r="B260" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C251" s="4" t="s">
+      <c r="C260" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D251" s="4" t="s">
+      <c r="D260" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E251" s="4" t="s">
+      <c r="E260" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F251" s="7" t="s">
+      <c r="F260" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G251" s="6" t="s">
+      <c r="G260" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H251" s="5" t="s">
+      <c r="H260" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I251" s="6" t="s">
+      <c r="I260" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J251" s="5" t="s">
+      <c r="J260" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K251" s="8" t="s">
+      <c r="K260" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="252">
-      <c r="A252" s="11" t="s">
-        <v>374</v>
-      </c>
-      <c r="B252" s="10" t="s">
+    <row r="261">
+      <c r="A261" s="11" t="s">
+        <v>387</v>
+      </c>
+      <c r="B261" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="C252" s="84"/>
-      <c r="D252" s="84"/>
-      <c r="E252" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F252" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="G252" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="H252" s="82"/>
-      <c r="I252" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="J252" s="144"/>
-      <c r="K252" s="82"/>
-    </row>
-    <row r="253">
-      <c r="A253" s="72">
+      <c r="C261" s="84"/>
+      <c r="D261" s="11">
+        <v>9.0</v>
+      </c>
+      <c r="E261" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F261" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="G261" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="H261" s="82"/>
+      <c r="I261" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="J261" s="144"/>
+      <c r="K261" s="82"/>
+    </row>
+    <row r="262">
+      <c r="A262" s="72">
         <v>40.0</v>
       </c>
-      <c r="B253" s="10" t="s">
-        <v>376</v>
-      </c>
-      <c r="C253" s="84"/>
-      <c r="D253" s="84"/>
-      <c r="E253" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F253" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="G253" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="H253" s="82"/>
-      <c r="I253" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="J253" s="144"/>
-      <c r="K253" s="82"/>
-    </row>
-    <row r="254">
-      <c r="A254" s="72">
+      <c r="B262" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="C262" s="84"/>
+      <c r="D262" s="11">
+        <v>6.0</v>
+      </c>
+      <c r="E262" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F262" s="12" t="s">
+        <v>390</v>
+      </c>
+      <c r="G262" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="H262" s="82"/>
+      <c r="I262" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="J262" s="144"/>
+      <c r="K262" s="82"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="72">
         <v>40.0</v>
       </c>
-      <c r="B254" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="C254" s="84"/>
-      <c r="D254" s="84"/>
-      <c r="E254" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F254" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="G254" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="H254" s="82"/>
-      <c r="I254" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="J254" s="144"/>
-      <c r="K254" s="82"/>
-    </row>
-    <row r="255">
-      <c r="A255" s="72">
+      <c r="B263" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="C263" s="84"/>
+      <c r="D263" s="11">
+        <v>9.0</v>
+      </c>
+      <c r="E263" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F263" s="12" t="s">
+        <v>392</v>
+      </c>
+      <c r="G263" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="H263" s="82"/>
+      <c r="I263" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="J263" s="144"/>
+      <c r="K263" s="82"/>
+    </row>
+    <row r="264">
+      <c r="A264" s="72">
         <v>40.0</v>
       </c>
-      <c r="B255" s="10" t="s">
-        <v>380</v>
-      </c>
-      <c r="C255" s="84"/>
-      <c r="D255" s="84"/>
-      <c r="E255" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F255" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="G255" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="H255" s="82"/>
-      <c r="I255" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="J255" s="144"/>
-      <c r="K255" s="82"/>
-    </row>
-    <row r="256">
-      <c r="A256" s="72">
+      <c r="B264" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C264" s="84"/>
+      <c r="D264" s="11">
+        <v>3.0</v>
+      </c>
+      <c r="E264" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F264" s="12" t="s">
+        <v>394</v>
+      </c>
+      <c r="G264" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="H264" s="82"/>
+      <c r="I264" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="J264" s="144"/>
+      <c r="K264" s="82"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="72">
         <v>40.0</v>
       </c>
-      <c r="B256" s="10" t="s">
-        <v>382</v>
-      </c>
-      <c r="C256" s="84"/>
-      <c r="D256" s="84"/>
-      <c r="E256" s="11" t="s">
-        <v>65</v>
-      </c>
-      <c r="F256" s="145" t="s">
-        <v>383</v>
-      </c>
-      <c r="G256" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="H256" s="88"/>
-      <c r="I256" s="86">
-        <v>45901.0</v>
-      </c>
-      <c r="J256" s="144"/>
-      <c r="K256" s="82"/>
-    </row>
-    <row r="257">
-      <c r="A257" s="6" t="s">
+      <c r="B265" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="C265" s="84"/>
+      <c r="D265" s="11">
+        <v>4.0</v>
+      </c>
+      <c r="E265" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="F265" s="145" t="s">
+        <v>396</v>
+      </c>
+      <c r="G265" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="H265" s="88"/>
+      <c r="I265" s="86">
+        <v>45901.0</v>
+      </c>
+      <c r="J265" s="144"/>
+      <c r="K265" s="82"/>
+    </row>
+    <row r="266">
+      <c r="A266" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B257" s="4"/>
-      <c r="C257" s="4"/>
-      <c r="D257" s="4"/>
-      <c r="E257" s="4"/>
-      <c r="F257" s="5"/>
-      <c r="G257" s="6" t="s">
+      <c r="B266" s="4"/>
+      <c r="C266" s="4"/>
+      <c r="D266" s="4"/>
+      <c r="E266" s="4"/>
+      <c r="F266" s="5"/>
+      <c r="G266" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H257" s="5"/>
-      <c r="I257" s="3" t="s">
+      <c r="H266" s="5"/>
+      <c r="I266" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J257" s="5"/>
-      <c r="K257" s="5"/>
-    </row>
-    <row r="258">
-      <c r="A258" s="6" t="s">
+      <c r="J266" s="5"/>
+      <c r="K266" s="5"/>
+    </row>
+    <row r="267">
+      <c r="A267" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B258" s="4" t="s">
+      <c r="B267" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C258" s="4" t="s">
+      <c r="C267" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D258" s="4" t="s">
+      <c r="D267" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E258" s="4" t="s">
+      <c r="E267" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F258" s="7" t="s">
+      <c r="F267" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G258" s="6" t="s">
+      <c r="G267" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H258" s="5" t="s">
+      <c r="H267" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I258" s="6" t="s">
+      <c r="I267" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J258" s="5" t="s">
+      <c r="J267" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K258" s="8" t="s">
+      <c r="K267" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="259">
-      <c r="A259" s="28" t="s">
-        <v>384</v>
-      </c>
-      <c r="B259" s="29" t="s">
+    <row r="268">
+      <c r="A268" s="28" t="s">
+        <v>397</v>
+      </c>
+      <c r="B268" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="C259" s="29"/>
-      <c r="D259" s="96"/>
-      <c r="E259" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="F259" s="30" t="s">
-        <v>385</v>
-      </c>
-      <c r="G259" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="H259" s="95"/>
-      <c r="I259" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="J259" s="146">
+      <c r="C268" s="29"/>
+      <c r="D268" s="29">
+        <v>5.0</v>
+      </c>
+      <c r="E268" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F268" s="30" t="s">
+        <v>398</v>
+      </c>
+      <c r="G268" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="H268" s="95"/>
+      <c r="I268" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="J268" s="146">
         <v>45915.0</v>
       </c>
-      <c r="K259" s="95"/>
-    </row>
-    <row r="260">
-      <c r="A260" s="33">
+      <c r="K268" s="95"/>
+    </row>
+    <row r="269">
+      <c r="A269" s="33">
         <v>41.0</v>
       </c>
-      <c r="B260" s="29" t="s">
-        <v>386</v>
-      </c>
-      <c r="C260" s="29"/>
-      <c r="D260" s="96"/>
-      <c r="E260" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="F260" s="30" t="s">
-        <v>387</v>
-      </c>
-      <c r="G260" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="H260" s="95"/>
-      <c r="I260" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="J260" s="146">
+      <c r="B269" s="29" t="s">
+        <v>399</v>
+      </c>
+      <c r="C269" s="29"/>
+      <c r="D269" s="29">
+        <v>6.0</v>
+      </c>
+      <c r="E269" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F269" s="30" t="s">
+        <v>400</v>
+      </c>
+      <c r="G269" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="H269" s="95"/>
+      <c r="I269" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="J269" s="146">
         <v>45915.0</v>
       </c>
-      <c r="K260" s="95"/>
-    </row>
-    <row r="261">
-      <c r="A261" s="33">
+      <c r="K269" s="95"/>
+    </row>
+    <row r="270">
+      <c r="A270" s="33">
         <v>41.0</v>
       </c>
-      <c r="B261" s="29" t="s">
-        <v>388</v>
-      </c>
-      <c r="C261" s="29"/>
-      <c r="D261" s="96"/>
-      <c r="E261" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="F261" s="30" t="s">
-        <v>389</v>
-      </c>
-      <c r="G261" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="H261" s="95"/>
-      <c r="I261" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="J261" s="146">
+      <c r="B270" s="29" t="s">
+        <v>401</v>
+      </c>
+      <c r="C270" s="29"/>
+      <c r="D270" s="29">
+        <v>3.0</v>
+      </c>
+      <c r="E270" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F270" s="30" t="s">
+        <v>402</v>
+      </c>
+      <c r="G270" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="H270" s="95"/>
+      <c r="I270" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="J270" s="146">
         <v>45915.0</v>
       </c>
-      <c r="K261" s="95"/>
-    </row>
-    <row r="262">
-      <c r="A262" s="33">
+      <c r="K270" s="95"/>
+    </row>
+    <row r="271">
+      <c r="A271" s="33">
         <v>41.0</v>
       </c>
-      <c r="B262" s="29" t="s">
-        <v>390</v>
-      </c>
-      <c r="C262" s="29"/>
-      <c r="D262" s="96"/>
-      <c r="E262" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="F262" s="30" t="s">
-        <v>391</v>
-      </c>
-      <c r="G262" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="H262" s="95"/>
-      <c r="I262" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="J262" s="146">
+      <c r="B271" s="29" t="s">
+        <v>403</v>
+      </c>
+      <c r="C271" s="29"/>
+      <c r="D271" s="29">
+        <v>3.0</v>
+      </c>
+      <c r="E271" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F271" s="30" t="s">
+        <v>404</v>
+      </c>
+      <c r="G271" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="H271" s="95"/>
+      <c r="I271" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="J271" s="146">
         <v>45915.0</v>
       </c>
-      <c r="K262" s="95"/>
-    </row>
-    <row r="263">
-      <c r="A263" s="33">
+      <c r="K271" s="95"/>
+    </row>
+    <row r="272">
+      <c r="A272" s="33">
         <v>41.0</v>
       </c>
-      <c r="B263" s="29" t="s">
-        <v>264</v>
-      </c>
-      <c r="C263" s="29"/>
-      <c r="D263" s="96"/>
-      <c r="E263" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="F263" s="142" t="s">
-        <v>392</v>
-      </c>
-      <c r="G263" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="H263" s="95"/>
-      <c r="I263" s="98">
-        <v>45901.0</v>
-      </c>
-      <c r="J263" s="146">
+      <c r="B272" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="C272" s="29"/>
+      <c r="D272" s="29">
+        <v>2.0</v>
+      </c>
+      <c r="E272" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="F272" s="140" t="s">
+        <v>405</v>
+      </c>
+      <c r="G272" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="H272" s="95"/>
+      <c r="I272" s="98">
+        <v>45901.0</v>
+      </c>
+      <c r="J272" s="146">
         <v>45915.0</v>
       </c>
-      <c r="K263" s="95"/>
-    </row>
-    <row r="264">
-      <c r="A264" s="6" t="s">
+      <c r="K272" s="95"/>
+    </row>
+    <row r="273">
+      <c r="A273" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B264" s="4"/>
-      <c r="C264" s="4"/>
-      <c r="D264" s="4"/>
-      <c r="E264" s="4"/>
-      <c r="F264" s="5"/>
-      <c r="G264" s="6" t="s">
+      <c r="B273" s="4"/>
+      <c r="C273" s="4"/>
+      <c r="D273" s="4"/>
+      <c r="E273" s="4"/>
+      <c r="F273" s="5"/>
+      <c r="G273" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H264" s="5"/>
-      <c r="I264" s="3" t="s">
+      <c r="H273" s="5"/>
+      <c r="I273" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J264" s="5"/>
-      <c r="K264" s="5"/>
-    </row>
-    <row r="265">
-      <c r="A265" s="6" t="s">
+      <c r="J273" s="5"/>
+      <c r="K273" s="5"/>
+    </row>
+    <row r="274">
+      <c r="A274" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B265" s="4" t="s">
+      <c r="B274" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C265" s="4" t="s">
+      <c r="C274" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D265" s="4" t="s">
+      <c r="D274" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E265" s="4" t="s">
+      <c r="E274" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F265" s="7" t="s">
+      <c r="F274" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G265" s="6" t="s">
+      <c r="G274" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H265" s="5" t="s">
+      <c r="H274" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I265" s="6" t="s">
+      <c r="I274" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J265" s="5" t="s">
+      <c r="J274" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K265" s="8" t="s">
+      <c r="K274" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="34" t="s">
-        <v>393</v>
-      </c>
-      <c r="B266" s="35" t="s">
+    <row r="275">
+      <c r="A275" s="34" t="s">
+        <v>406</v>
+      </c>
+      <c r="B275" s="35" t="s">
         <v>135</v>
       </c>
-      <c r="C266" s="101"/>
-      <c r="D266" s="101"/>
-      <c r="E266" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="F266" s="36" t="s">
-        <v>394</v>
-      </c>
-      <c r="G266" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="H266" s="100"/>
-      <c r="I266" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="J266" s="100"/>
-      <c r="K266" s="100"/>
-    </row>
-    <row r="267">
-      <c r="A267" s="39">
+      <c r="C275" s="101"/>
+      <c r="D275" s="35">
+        <v>7.0</v>
+      </c>
+      <c r="E275" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="F275" s="36" t="s">
+        <v>407</v>
+      </c>
+      <c r="G275" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="H275" s="100"/>
+      <c r="I275" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="J275" s="100"/>
+      <c r="K275" s="100"/>
+    </row>
+    <row r="276">
+      <c r="A276" s="39">
         <v>44.0</v>
       </c>
-      <c r="B267" s="35" t="s">
-        <v>395</v>
-      </c>
-      <c r="C267" s="101"/>
-      <c r="D267" s="101"/>
-      <c r="E267" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="F267" s="36" t="s">
-        <v>396</v>
-      </c>
-      <c r="G267" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="H267" s="100"/>
-      <c r="I267" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="J267" s="100"/>
-      <c r="K267" s="100"/>
-    </row>
-    <row r="268">
-      <c r="A268" s="39">
+      <c r="B276" s="35" t="s">
+        <v>408</v>
+      </c>
+      <c r="C276" s="101"/>
+      <c r="D276" s="35">
+        <v>4.0</v>
+      </c>
+      <c r="E276" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="F276" s="36" t="s">
+        <v>409</v>
+      </c>
+      <c r="G276" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="H276" s="100"/>
+      <c r="I276" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="J276" s="100"/>
+      <c r="K276" s="100"/>
+    </row>
+    <row r="277">
+      <c r="A277" s="39">
         <v>44.0</v>
       </c>
-      <c r="B268" s="35" t="s">
-        <v>397</v>
-      </c>
-      <c r="C268" s="101"/>
-      <c r="D268" s="101"/>
-      <c r="E268" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="F268" s="36" t="s">
-        <v>398</v>
-      </c>
-      <c r="G268" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="H268" s="100"/>
-      <c r="I268" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="J268" s="100"/>
-      <c r="K268" s="100"/>
-    </row>
-    <row r="269">
-      <c r="A269" s="39">
+      <c r="B277" s="35" t="s">
+        <v>410</v>
+      </c>
+      <c r="C277" s="101"/>
+      <c r="D277" s="35">
+        <v>6.0</v>
+      </c>
+      <c r="E277" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="F277" s="36" t="s">
+        <v>411</v>
+      </c>
+      <c r="G277" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="H277" s="100"/>
+      <c r="I277" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="J277" s="100"/>
+      <c r="K277" s="100"/>
+    </row>
+    <row r="278">
+      <c r="A278" s="39">
         <v>44.0</v>
       </c>
-      <c r="B269" s="35" t="s">
-        <v>399</v>
-      </c>
-      <c r="C269" s="101"/>
-      <c r="D269" s="101"/>
-      <c r="E269" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="F269" s="36" t="s">
-        <v>400</v>
-      </c>
-      <c r="G269" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="H269" s="100"/>
-      <c r="I269" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="J269" s="100"/>
-      <c r="K269" s="100"/>
-    </row>
-    <row r="270">
-      <c r="A270" s="39">
+      <c r="B278" s="35" t="s">
+        <v>412</v>
+      </c>
+      <c r="C278" s="101"/>
+      <c r="D278" s="35">
+        <v>3.0</v>
+      </c>
+      <c r="E278" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="F278" s="36" t="s">
+        <v>413</v>
+      </c>
+      <c r="G278" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="H278" s="100"/>
+      <c r="I278" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="J278" s="100"/>
+      <c r="K278" s="100"/>
+    </row>
+    <row r="279">
+      <c r="A279" s="39">
         <v>44.0</v>
       </c>
-      <c r="B270" s="35" t="s">
-        <v>401</v>
-      </c>
-      <c r="C270" s="101"/>
-      <c r="D270" s="101"/>
-      <c r="E270" s="35" t="s">
-        <v>65</v>
-      </c>
-      <c r="F270" s="40" t="s">
-        <v>402</v>
-      </c>
-      <c r="G270" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="H270" s="100"/>
-      <c r="I270" s="102">
-        <v>45901.0</v>
-      </c>
-      <c r="J270" s="100"/>
-      <c r="K270" s="100"/>
-    </row>
-    <row r="271">
-      <c r="A271" s="3">
+      <c r="B279" s="35" t="s">
+        <v>414</v>
+      </c>
+      <c r="C279" s="101"/>
+      <c r="D279" s="35">
+        <v>4.0</v>
+      </c>
+      <c r="E279" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="F279" s="36" t="s">
+        <v>415</v>
+      </c>
+      <c r="G279" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="H279" s="100"/>
+      <c r="I279" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="J279" s="100"/>
+      <c r="K279" s="100"/>
+    </row>
+    <row r="280">
+      <c r="A280" s="39">
         <v>44.0</v>
       </c>
-      <c r="B271" s="25" t="s">
+      <c r="B280" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="C271" s="4"/>
-      <c r="D271" s="4"/>
-      <c r="E271" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="F271" s="8" t="s">
-        <v>403</v>
-      </c>
-      <c r="G271" s="6" t="s">
+      <c r="C280" s="101"/>
+      <c r="D280" s="35">
+        <v>2.0</v>
+      </c>
+      <c r="E280" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="F280" s="40" t="s">
+        <v>416</v>
+      </c>
+      <c r="G280" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="H280" s="100"/>
+      <c r="I280" s="102">
+        <v>45901.0</v>
+      </c>
+      <c r="J280" s="100"/>
+      <c r="K280" s="100"/>
+    </row>
+    <row r="281">
+      <c r="A281" s="3">
+        <v>44.0</v>
+      </c>
+      <c r="B281" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C281" s="4"/>
+      <c r="D281" s="4"/>
+      <c r="E281" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="F281" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="G281" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H271" s="5"/>
-      <c r="I271" s="3" t="s">
+      <c r="H281" s="5"/>
+      <c r="I281" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J271" s="5"/>
-      <c r="K271" s="5"/>
-    </row>
-    <row r="272">
-      <c r="A272" s="6" t="s">
+      <c r="J281" s="5"/>
+      <c r="K281" s="5"/>
+    </row>
+    <row r="282">
+      <c r="A282" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B272" s="4" t="s">
+      <c r="B282" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C272" s="4" t="s">
+      <c r="C282" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D272" s="4" t="s">
+      <c r="D282" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E272" s="4" t="s">
+      <c r="E282" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F272" s="7" t="s">
+      <c r="F282" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G272" s="6" t="s">
+      <c r="G282" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H272" s="5" t="s">
+      <c r="H282" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I272" s="6" t="s">
+      <c r="I282" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J272" s="5" t="s">
+      <c r="J282" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K272" s="8" t="s">
+      <c r="K282" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="46" t="s">
-        <v>404</v>
-      </c>
-      <c r="B273" s="42" t="s">
+    <row r="283">
+      <c r="A283" s="46" t="s">
+        <v>417</v>
+      </c>
+      <c r="B283" s="42" t="s">
         <v>135</v>
       </c>
-      <c r="C273" s="105"/>
-      <c r="D273" s="105"/>
-      <c r="E273" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="F273" s="43" t="s">
-        <v>405</v>
-      </c>
-      <c r="G273" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="H273" s="107"/>
-      <c r="I273" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="J273" s="107"/>
-      <c r="K273" s="107"/>
-    </row>
-    <row r="274">
-      <c r="A274" s="46">
+      <c r="C283" s="105"/>
+      <c r="D283" s="42">
+        <v>8.0</v>
+      </c>
+      <c r="E283" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="F283" s="43" t="s">
+        <v>418</v>
+      </c>
+      <c r="G283" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="H283" s="107"/>
+      <c r="I283" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="J283" s="107"/>
+      <c r="K283" s="107"/>
+    </row>
+    <row r="284">
+      <c r="A284" s="46">
         <v>45.0</v>
       </c>
-      <c r="B274" s="42" t="s">
-        <v>406</v>
-      </c>
-      <c r="C274" s="105"/>
-      <c r="D274" s="105"/>
-      <c r="E274" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="F274" s="43" t="s">
-        <v>407</v>
-      </c>
-      <c r="G274" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="H274" s="107"/>
-      <c r="I274" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="J274" s="107"/>
-      <c r="K274" s="107"/>
-    </row>
-    <row r="275">
-      <c r="A275" s="46">
+      <c r="B284" s="42" t="s">
+        <v>419</v>
+      </c>
+      <c r="C284" s="105"/>
+      <c r="D284" s="42">
+        <v>5.0</v>
+      </c>
+      <c r="E284" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="F284" s="43" t="s">
+        <v>420</v>
+      </c>
+      <c r="G284" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="H284" s="107"/>
+      <c r="I284" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="J284" s="107"/>
+      <c r="K284" s="107"/>
+    </row>
+    <row r="285">
+      <c r="A285" s="46">
         <v>45.0</v>
       </c>
-      <c r="B275" s="42" t="s">
-        <v>408</v>
-      </c>
-      <c r="C275" s="105"/>
-      <c r="D275" s="105"/>
-      <c r="E275" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="F275" s="43" t="s">
-        <v>409</v>
-      </c>
-      <c r="G275" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="H275" s="107"/>
-      <c r="I275" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="J275" s="107"/>
-      <c r="K275" s="107"/>
-    </row>
-    <row r="276">
-      <c r="A276" s="46">
+      <c r="B285" s="42" t="s">
+        <v>421</v>
+      </c>
+      <c r="C285" s="105"/>
+      <c r="D285" s="42">
+        <v>6.0</v>
+      </c>
+      <c r="E285" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="F285" s="43" t="s">
+        <v>422</v>
+      </c>
+      <c r="G285" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="H285" s="107"/>
+      <c r="I285" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="J285" s="107"/>
+      <c r="K285" s="107"/>
+    </row>
+    <row r="286">
+      <c r="A286" s="46">
         <v>45.0</v>
       </c>
-      <c r="B276" s="42" t="s">
-        <v>410</v>
-      </c>
-      <c r="C276" s="105"/>
-      <c r="D276" s="105"/>
-      <c r="E276" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="F276" s="43" t="s">
-        <v>411</v>
-      </c>
-      <c r="G276" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="H276" s="107"/>
-      <c r="I276" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="J276" s="107"/>
-      <c r="K276" s="107"/>
-    </row>
-    <row r="277">
-      <c r="A277" s="46">
+      <c r="B286" s="42" t="s">
+        <v>423</v>
+      </c>
+      <c r="C286" s="105"/>
+      <c r="D286" s="42">
+        <v>3.0</v>
+      </c>
+      <c r="E286" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="F286" s="43" t="s">
+        <v>424</v>
+      </c>
+      <c r="G286" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="H286" s="107"/>
+      <c r="I286" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="J286" s="107"/>
+      <c r="K286" s="107"/>
+    </row>
+    <row r="287">
+      <c r="A287" s="46">
         <v>45.0</v>
       </c>
-      <c r="B277" s="42" t="s">
-        <v>412</v>
-      </c>
-      <c r="C277" s="105"/>
-      <c r="D277" s="105"/>
-      <c r="E277" s="42" t="s">
-        <v>65</v>
-      </c>
-      <c r="F277" s="110" t="s">
-        <v>413</v>
-      </c>
-      <c r="G277" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="H277" s="107"/>
-      <c r="I277" s="106">
-        <v>45901.0</v>
-      </c>
-      <c r="J277" s="107"/>
-      <c r="K277" s="107"/>
-    </row>
-    <row r="278">
-      <c r="A278" s="3">
+      <c r="B287" s="42" t="s">
+        <v>425</v>
+      </c>
+      <c r="C287" s="105"/>
+      <c r="D287" s="42">
+        <v>3.0</v>
+      </c>
+      <c r="E287" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="F287" s="43" t="s">
+        <v>426</v>
+      </c>
+      <c r="G287" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="H287" s="107"/>
+      <c r="I287" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="J287" s="107"/>
+      <c r="K287" s="107"/>
+    </row>
+    <row r="288">
+      <c r="A288" s="46">
         <v>45.0</v>
       </c>
-      <c r="B278" s="25" t="s">
-        <v>414</v>
-      </c>
-      <c r="C278" s="4"/>
-      <c r="D278" s="4"/>
-      <c r="E278" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="F278" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="G278" s="6" t="s">
+      <c r="B288" s="42" t="s">
+        <v>427</v>
+      </c>
+      <c r="C288" s="105"/>
+      <c r="D288" s="42">
+        <v>4.0</v>
+      </c>
+      <c r="E288" s="42" t="s">
+        <v>65</v>
+      </c>
+      <c r="F288" s="110" t="s">
+        <v>428</v>
+      </c>
+      <c r="G288" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="H288" s="107"/>
+      <c r="I288" s="106">
+        <v>45901.0</v>
+      </c>
+      <c r="J288" s="107"/>
+      <c r="K288" s="107"/>
+    </row>
+    <row r="289">
+      <c r="A289" s="3">
+        <v>45.0</v>
+      </c>
+      <c r="B289" s="25" t="s">
+        <v>427</v>
+      </c>
+      <c r="C289" s="4"/>
+      <c r="D289" s="4"/>
+      <c r="E289" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="F289" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="G289" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H278" s="5"/>
-      <c r="I278" s="3" t="s">
+      <c r="H289" s="5"/>
+      <c r="I289" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J278" s="5"/>
-      <c r="K278" s="5"/>
-    </row>
-    <row r="279">
-      <c r="A279" s="6" t="s">
+      <c r="J289" s="5"/>
+      <c r="K289" s="5"/>
+    </row>
+    <row r="290">
+      <c r="A290" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B279" s="4" t="s">
+      <c r="B290" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C279" s="4" t="s">
+      <c r="C290" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D279" s="4" t="s">
+      <c r="D290" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E279" s="4" t="s">
+      <c r="E290" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F279" s="7" t="s">
+      <c r="F290" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G279" s="6" t="s">
+      <c r="G290" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H279" s="5" t="s">
+      <c r="H290" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I279" s="6" t="s">
+      <c r="I290" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J279" s="5" t="s">
+      <c r="J290" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K279" s="8" t="s">
+      <c r="K290" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="280">
-      <c r="A280" s="73" t="s">
-        <v>416</v>
-      </c>
-      <c r="B280" s="74" t="s">
+    <row r="291">
+      <c r="A291" s="73" t="s">
+        <v>429</v>
+      </c>
+      <c r="B291" s="74" t="s">
         <v>135</v>
       </c>
-      <c r="C280" s="123"/>
-      <c r="D280" s="123"/>
-      <c r="E280" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F280" s="75" t="s">
-        <v>417</v>
-      </c>
-      <c r="G280" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="H280" s="125"/>
-      <c r="I280" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="J280" s="125"/>
-      <c r="K280" s="125"/>
-    </row>
-    <row r="281">
-      <c r="A281" s="73">
+      <c r="C291" s="122"/>
+      <c r="D291" s="74">
+        <v>5.0</v>
+      </c>
+      <c r="E291" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F291" s="75" t="s">
+        <v>430</v>
+      </c>
+      <c r="G291" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H291" s="124"/>
+      <c r="I291" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J291" s="124"/>
+      <c r="K291" s="124"/>
+    </row>
+    <row r="292">
+      <c r="A292" s="73">
         <v>46.0</v>
       </c>
-      <c r="B281" s="74" t="s">
-        <v>418</v>
-      </c>
-      <c r="C281" s="123"/>
-      <c r="D281" s="123"/>
-      <c r="E281" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F281" s="75" t="s">
-        <v>419</v>
-      </c>
-      <c r="G281" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="H281" s="125"/>
-      <c r="I281" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="J281" s="125"/>
-      <c r="K281" s="125"/>
-    </row>
-    <row r="282">
-      <c r="A282" s="73">
+      <c r="B292" s="74" t="s">
+        <v>431</v>
+      </c>
+      <c r="C292" s="122"/>
+      <c r="D292" s="74">
+        <v>4.0</v>
+      </c>
+      <c r="E292" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F292" s="75" t="s">
+        <v>432</v>
+      </c>
+      <c r="G292" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H292" s="124"/>
+      <c r="I292" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J292" s="124"/>
+      <c r="K292" s="124"/>
+    </row>
+    <row r="293">
+      <c r="A293" s="73">
         <v>46.0</v>
       </c>
-      <c r="B282" s="74" t="s">
-        <v>420</v>
-      </c>
-      <c r="C282" s="123"/>
-      <c r="D282" s="123"/>
-      <c r="E282" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F282" s="75" t="s">
-        <v>421</v>
-      </c>
-      <c r="G282" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="H282" s="125"/>
-      <c r="I282" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="J282" s="125"/>
-      <c r="K282" s="125"/>
-    </row>
-    <row r="283">
-      <c r="A283" s="73">
+      <c r="B293" s="74" t="s">
+        <v>433</v>
+      </c>
+      <c r="C293" s="122"/>
+      <c r="D293" s="74">
+        <v>5.0</v>
+      </c>
+      <c r="E293" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F293" s="75" t="s">
+        <v>434</v>
+      </c>
+      <c r="G293" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H293" s="124"/>
+      <c r="I293" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J293" s="124"/>
+      <c r="K293" s="124"/>
+    </row>
+    <row r="294">
+      <c r="A294" s="73">
         <v>46.0</v>
       </c>
-      <c r="B283" s="74" t="s">
-        <v>422</v>
-      </c>
-      <c r="C283" s="123"/>
-      <c r="D283" s="123"/>
-      <c r="E283" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F283" s="75" t="s">
-        <v>423</v>
-      </c>
-      <c r="G283" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="H283" s="125"/>
-      <c r="I283" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="J283" s="125"/>
-      <c r="K283" s="125"/>
-    </row>
-    <row r="284">
-      <c r="A284" s="73">
+      <c r="B294" s="74" t="s">
+        <v>435</v>
+      </c>
+      <c r="C294" s="122"/>
+      <c r="D294" s="74">
+        <v>3.0</v>
+      </c>
+      <c r="E294" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F294" s="75" t="s">
+        <v>436</v>
+      </c>
+      <c r="G294" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H294" s="124"/>
+      <c r="I294" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J294" s="124"/>
+      <c r="K294" s="124"/>
+    </row>
+    <row r="295">
+      <c r="A295" s="73">
         <v>46.0</v>
       </c>
-      <c r="B284" s="74" t="s">
-        <v>424</v>
-      </c>
-      <c r="C284" s="123"/>
-      <c r="D284" s="123"/>
-      <c r="E284" s="74" t="s">
-        <v>65</v>
-      </c>
-      <c r="F284" s="126" t="s">
-        <v>425</v>
-      </c>
-      <c r="G284" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="H284" s="125"/>
-      <c r="I284" s="124">
-        <v>45901.0</v>
-      </c>
-      <c r="J284" s="125"/>
-      <c r="K284" s="125"/>
-    </row>
-    <row r="285">
-      <c r="A285" s="6" t="s">
+      <c r="B295" s="74" t="s">
+        <v>437</v>
+      </c>
+      <c r="C295" s="122"/>
+      <c r="D295" s="74">
+        <v>2.0</v>
+      </c>
+      <c r="E295" s="74" t="s">
+        <v>65</v>
+      </c>
+      <c r="F295" s="125" t="s">
+        <v>438</v>
+      </c>
+      <c r="G295" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="H295" s="124"/>
+      <c r="I295" s="123">
+        <v>45901.0</v>
+      </c>
+      <c r="J295" s="124"/>
+      <c r="K295" s="124"/>
+    </row>
+    <row r="296">
+      <c r="A296" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B285" s="4"/>
-      <c r="C285" s="4"/>
-      <c r="D285" s="4"/>
-      <c r="E285" s="4"/>
-      <c r="F285" s="5"/>
-      <c r="G285" s="6" t="s">
+      <c r="B296" s="4"/>
+      <c r="C296" s="4"/>
+      <c r="D296" s="4"/>
+      <c r="E296" s="4"/>
+      <c r="F296" s="5"/>
+      <c r="G296" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H285" s="5"/>
-      <c r="I285" s="3" t="s">
+      <c r="H296" s="5"/>
+      <c r="I296" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J285" s="5"/>
-      <c r="K285" s="5"/>
-    </row>
-    <row r="286">
-      <c r="A286" s="6" t="s">
+      <c r="J296" s="5"/>
+      <c r="K296" s="5"/>
+    </row>
+    <row r="297">
+      <c r="A297" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B286" s="4" t="s">
+      <c r="B297" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C286" s="4" t="s">
+      <c r="C297" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D286" s="4" t="s">
+      <c r="D297" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E286" s="4" t="s">
+      <c r="E297" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F286" s="7" t="s">
+      <c r="F297" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G286" s="6" t="s">
+      <c r="G297" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H286" s="5" t="s">
+      <c r="H297" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I286" s="6" t="s">
+      <c r="I297" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J286" s="5" t="s">
+      <c r="J297" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K286" s="8" t="s">
+      <c r="K297" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="287">
-      <c r="A287" s="65" t="s">
-        <v>426</v>
-      </c>
-      <c r="B287" s="66" t="s">
+    <row r="298">
+      <c r="A298" s="65" t="s">
+        <v>439</v>
+      </c>
+      <c r="B298" s="66" t="s">
         <v>135</v>
       </c>
-      <c r="C287" s="119"/>
-      <c r="D287" s="119"/>
-      <c r="E287" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="F287" s="67" t="s">
-        <v>427</v>
-      </c>
-      <c r="G287" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H287" s="121"/>
-      <c r="I287" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="J287" s="121"/>
-      <c r="K287" s="121"/>
-    </row>
-    <row r="288">
-      <c r="A288" s="65">
+      <c r="C298" s="143"/>
+      <c r="D298" s="66">
+        <v>4.0</v>
+      </c>
+      <c r="E298" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F298" s="67" t="s">
+        <v>440</v>
+      </c>
+      <c r="G298" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H298" s="120"/>
+      <c r="I298" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="J298" s="120"/>
+      <c r="K298" s="120"/>
+    </row>
+    <row r="299">
+      <c r="A299" s="65">
         <v>49.0</v>
       </c>
-      <c r="B288" s="66" t="s">
-        <v>428</v>
-      </c>
-      <c r="C288" s="119"/>
-      <c r="D288" s="119"/>
-      <c r="E288" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="F288" s="67" t="s">
-        <v>429</v>
-      </c>
-      <c r="G288" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H288" s="121"/>
-      <c r="I288" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="J288" s="121"/>
-      <c r="K288" s="121"/>
-    </row>
-    <row r="289">
-      <c r="A289" s="65">
+      <c r="B299" s="66" t="s">
+        <v>441</v>
+      </c>
+      <c r="C299" s="143"/>
+      <c r="D299" s="66">
+        <v>3.0</v>
+      </c>
+      <c r="E299" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F299" s="67" t="s">
+        <v>442</v>
+      </c>
+      <c r="G299" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H299" s="120"/>
+      <c r="I299" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="J299" s="120"/>
+      <c r="K299" s="120"/>
+    </row>
+    <row r="300">
+      <c r="A300" s="65">
         <v>49.0</v>
       </c>
-      <c r="B289" s="66" t="s">
-        <v>430</v>
-      </c>
-      <c r="C289" s="119"/>
-      <c r="D289" s="119"/>
-      <c r="E289" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="F289" s="67" t="s">
-        <v>431</v>
-      </c>
-      <c r="G289" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H289" s="121"/>
-      <c r="I289" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="J289" s="121"/>
-      <c r="K289" s="121"/>
-    </row>
-    <row r="290">
-      <c r="A290" s="65">
+      <c r="B300" s="66" t="s">
+        <v>443</v>
+      </c>
+      <c r="C300" s="143"/>
+      <c r="D300" s="66">
+        <v>6.0</v>
+      </c>
+      <c r="E300" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F300" s="67" t="s">
+        <v>444</v>
+      </c>
+      <c r="G300" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H300" s="120"/>
+      <c r="I300" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="J300" s="120"/>
+      <c r="K300" s="120"/>
+    </row>
+    <row r="301">
+      <c r="A301" s="65">
         <v>49.0</v>
       </c>
-      <c r="B290" s="66" t="s">
-        <v>432</v>
-      </c>
-      <c r="C290" s="119"/>
-      <c r="D290" s="119"/>
-      <c r="E290" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="F290" s="67" t="s">
-        <v>433</v>
-      </c>
-      <c r="G290" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H290" s="121"/>
-      <c r="I290" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="J290" s="121"/>
-      <c r="K290" s="121"/>
-    </row>
-    <row r="291">
-      <c r="A291" s="65">
+      <c r="B301" s="66" t="s">
+        <v>445</v>
+      </c>
+      <c r="C301" s="143"/>
+      <c r="D301" s="66">
+        <v>3.0</v>
+      </c>
+      <c r="E301" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F301" s="67" t="s">
+        <v>446</v>
+      </c>
+      <c r="G301" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H301" s="120"/>
+      <c r="I301" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="J301" s="120"/>
+      <c r="K301" s="120"/>
+    </row>
+    <row r="302">
+      <c r="A302" s="65">
         <v>49.0</v>
       </c>
-      <c r="B291" s="66" t="s">
-        <v>434</v>
-      </c>
-      <c r="C291" s="119"/>
-      <c r="D291" s="119"/>
-      <c r="E291" s="66" t="s">
-        <v>65</v>
-      </c>
-      <c r="F291" s="122" t="s">
-        <v>435</v>
-      </c>
-      <c r="G291" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="H291" s="121"/>
-      <c r="I291" s="120">
-        <v>45901.0</v>
-      </c>
-      <c r="J291" s="121"/>
-      <c r="K291" s="121"/>
-    </row>
-    <row r="292">
-      <c r="A292" s="6" t="s">
+      <c r="B302" s="66" t="s">
+        <v>447</v>
+      </c>
+      <c r="C302" s="143"/>
+      <c r="D302" s="66">
+        <v>3.0</v>
+      </c>
+      <c r="E302" s="66" t="s">
+        <v>65</v>
+      </c>
+      <c r="F302" s="121" t="s">
+        <v>448</v>
+      </c>
+      <c r="G302" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="H302" s="120"/>
+      <c r="I302" s="119">
+        <v>45901.0</v>
+      </c>
+      <c r="J302" s="120"/>
+      <c r="K302" s="120"/>
+    </row>
+    <row r="303">
+      <c r="A303" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B292" s="4"/>
-      <c r="C292" s="4"/>
-      <c r="D292" s="4"/>
-      <c r="E292" s="4"/>
-      <c r="F292" s="5"/>
-      <c r="G292" s="6" t="s">
+      <c r="B303" s="4"/>
+      <c r="C303" s="4"/>
+      <c r="D303" s="4"/>
+      <c r="E303" s="4"/>
+      <c r="F303" s="5"/>
+      <c r="G303" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H292" s="5"/>
-      <c r="I292" s="3" t="s">
+      <c r="H303" s="5"/>
+      <c r="I303" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J292" s="5"/>
-      <c r="K292" s="5"/>
-    </row>
-    <row r="293">
-      <c r="A293" s="6" t="s">
+      <c r="J303" s="5"/>
+      <c r="K303" s="5"/>
+    </row>
+    <row r="304">
+      <c r="A304" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B293" s="4" t="s">
+      <c r="B304" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C293" s="4" t="s">
+      <c r="C304" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D293" s="4" t="s">
+      <c r="D304" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E293" s="4" t="s">
+      <c r="E304" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F293" s="7" t="s">
+      <c r="F304" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G293" s="6" t="s">
+      <c r="G304" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H293" s="5" t="s">
+      <c r="H304" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="I293" s="6" t="s">
+      <c r="I304" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="J293" s="5" t="s">
+      <c r="J304" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K293" s="8" t="s">
+      <c r="K304" s="8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="294">
-      <c r="A294" s="129" t="s">
-        <v>436</v>
-      </c>
-      <c r="B294" s="130" t="s">
+    <row r="305">
+      <c r="A305" s="128" t="s">
+        <v>449</v>
+      </c>
+      <c r="B305" s="129" t="s">
         <v>135</v>
       </c>
-      <c r="C294" s="131"/>
-      <c r="D294" s="131"/>
-      <c r="E294" s="130" t="s">
-        <v>65</v>
-      </c>
-      <c r="F294" s="132" t="s">
-        <v>437</v>
-      </c>
-      <c r="G294" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="H294" s="134"/>
-      <c r="I294" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="J294" s="134"/>
-      <c r="K294" s="134"/>
-    </row>
-    <row r="295">
-      <c r="A295" s="129">
+      <c r="C305" s="142"/>
+      <c r="D305" s="129">
+        <v>4.0</v>
+      </c>
+      <c r="E305" s="129" t="s">
+        <v>65</v>
+      </c>
+      <c r="F305" s="130" t="s">
+        <v>450</v>
+      </c>
+      <c r="G305" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="H305" s="132"/>
+      <c r="I305" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="J305" s="132"/>
+      <c r="K305" s="132"/>
+    </row>
+    <row r="306">
+      <c r="A306" s="128">
         <v>51.0</v>
       </c>
-      <c r="B295" s="130" t="s">
-        <v>438</v>
-      </c>
-      <c r="C295" s="131"/>
-      <c r="D295" s="131"/>
-      <c r="E295" s="130" t="s">
-        <v>65</v>
-      </c>
-      <c r="F295" s="132" t="s">
-        <v>439</v>
-      </c>
-      <c r="G295" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="H295" s="134"/>
-      <c r="I295" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="J295" s="134"/>
-      <c r="K295" s="134"/>
-    </row>
-    <row r="296">
-      <c r="A296" s="129">
+      <c r="B306" s="129" t="s">
+        <v>451</v>
+      </c>
+      <c r="C306" s="142"/>
+      <c r="D306" s="129">
+        <v>6.0</v>
+      </c>
+      <c r="E306" s="129" t="s">
+        <v>65</v>
+      </c>
+      <c r="F306" s="130" t="s">
+        <v>452</v>
+      </c>
+      <c r="G306" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="H306" s="132"/>
+      <c r="I306" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="J306" s="132"/>
+      <c r="K306" s="132"/>
+    </row>
+    <row r="307">
+      <c r="A307" s="128">
         <v>51.0</v>
       </c>
-      <c r="B296" s="130" t="s">
-        <v>230</v>
-      </c>
-      <c r="C296" s="131"/>
-      <c r="D296" s="131"/>
-      <c r="E296" s="130" t="s">
-        <v>65</v>
-      </c>
-      <c r="F296" s="132" t="s">
-        <v>440</v>
-      </c>
-      <c r="G296" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="H296" s="134"/>
-      <c r="I296" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="J296" s="134"/>
-      <c r="K296" s="134"/>
-    </row>
-    <row r="297">
-      <c r="A297" s="129">
+      <c r="B307" s="129" t="s">
+        <v>233</v>
+      </c>
+      <c r="C307" s="142"/>
+      <c r="D307" s="129">
+        <v>5.0</v>
+      </c>
+      <c r="E307" s="129" t="s">
+        <v>65</v>
+      </c>
+      <c r="F307" s="130" t="s">
+        <v>453</v>
+      </c>
+      <c r="G307" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="H307" s="132"/>
+      <c r="I307" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="J307" s="132"/>
+      <c r="K307" s="132"/>
+    </row>
+    <row r="308">
+      <c r="A308" s="128">
         <v>51.0</v>
       </c>
-      <c r="B297" s="130" t="s">
-        <v>441</v>
-      </c>
-      <c r="C297" s="131"/>
-      <c r="D297" s="131"/>
-      <c r="E297" s="130" t="s">
-        <v>65</v>
-      </c>
-      <c r="F297" s="132" t="s">
-        <v>442</v>
-      </c>
-      <c r="G297" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="H297" s="134"/>
-      <c r="I297" s="133">
-        <v>45901.0</v>
-      </c>
-      <c r="J297" s="134"/>
-      <c r="K297" s="134"/>
-    </row>
-    <row r="298">
-      <c r="A298" s="147">
+      <c r="B308" s="129" t="s">
+        <v>454</v>
+      </c>
+      <c r="C308" s="142"/>
+      <c r="D308" s="129">
+        <v>3.0</v>
+      </c>
+      <c r="E308" s="129" t="s">
+        <v>65</v>
+      </c>
+      <c r="F308" s="130" t="s">
+        <v>455</v>
+      </c>
+      <c r="G308" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="H308" s="132"/>
+      <c r="I308" s="131">
+        <v>45901.0</v>
+      </c>
+      <c r="J308" s="132"/>
+      <c r="K308" s="132"/>
+    </row>
+    <row r="309">
+      <c r="A309" s="147">
         <v>51.0</v>
       </c>
-      <c r="B298" s="148" t="s">
-        <v>443</v>
-      </c>
-      <c r="C298" s="149"/>
-      <c r="D298" s="149"/>
-      <c r="E298" s="148" t="s">
-        <v>65</v>
-      </c>
-      <c r="F298" s="137" t="s">
-        <v>444</v>
-      </c>
-      <c r="G298" s="150">
-        <v>45901.0</v>
-      </c>
-      <c r="H298" s="151"/>
-      <c r="I298" s="150">
-        <v>45901.0</v>
-      </c>
-      <c r="J298" s="151"/>
-      <c r="K298" s="151"/>
-    </row>
-    <row r="299">
-      <c r="A299" s="152"/>
-      <c r="B299" s="152"/>
-      <c r="C299" s="152"/>
-      <c r="D299" s="152"/>
-      <c r="E299" s="152"/>
-      <c r="F299" s="152"/>
-      <c r="G299" s="152"/>
-      <c r="H299" s="152"/>
-      <c r="I299" s="153"/>
-      <c r="J299" s="152"/>
-      <c r="K299" s="152"/>
-    </row>
-    <row r="300">
-      <c r="A300" s="152"/>
-      <c r="B300" s="152"/>
-      <c r="C300" s="152"/>
-      <c r="D300" s="152"/>
-      <c r="E300" s="152"/>
-      <c r="F300" s="152"/>
-      <c r="G300" s="152"/>
-      <c r="H300" s="152"/>
-      <c r="I300" s="152"/>
-      <c r="J300" s="152"/>
-      <c r="K300" s="153"/>
-    </row>
-    <row r="301">
-      <c r="E301" s="152"/>
-      <c r="F301" s="152"/>
-      <c r="G301" s="154"/>
-      <c r="H301" s="152"/>
-      <c r="I301" s="154"/>
-      <c r="J301" s="152"/>
-      <c r="K301" s="152"/>
-    </row>
-    <row r="302">
-      <c r="A302" s="155" t="s">
+      <c r="B309" s="148" t="s">
+        <v>456</v>
+      </c>
+      <c r="C309" s="149"/>
+      <c r="D309" s="148">
+        <v>3.0</v>
+      </c>
+      <c r="E309" s="148" t="s">
+        <v>65</v>
+      </c>
+      <c r="F309" s="135" t="s">
+        <v>457</v>
+      </c>
+      <c r="G309" s="150">
+        <v>45901.0</v>
+      </c>
+      <c r="H309" s="151"/>
+      <c r="I309" s="150">
+        <v>45901.0</v>
+      </c>
+      <c r="J309" s="151"/>
+      <c r="K309" s="151"/>
+    </row>
+    <row r="310">
+      <c r="A310" s="152"/>
+      <c r="B310" s="152"/>
+      <c r="C310" s="152"/>
+      <c r="D310" s="152"/>
+      <c r="E310" s="152"/>
+      <c r="F310" s="152"/>
+      <c r="G310" s="152"/>
+      <c r="H310" s="152"/>
+      <c r="I310" s="153"/>
+      <c r="J310" s="152"/>
+      <c r="K310" s="152"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="152"/>
+      <c r="B311" s="152"/>
+      <c r="C311" s="152"/>
+      <c r="D311" s="152"/>
+      <c r="E311" s="152"/>
+      <c r="F311" s="152"/>
+      <c r="G311" s="152"/>
+      <c r="H311" s="152"/>
+      <c r="I311" s="152"/>
+      <c r="J311" s="152"/>
+      <c r="K311" s="153"/>
+    </row>
+    <row r="312">
+      <c r="E312" s="152"/>
+      <c r="F312" s="152"/>
+      <c r="G312" s="154"/>
+      <c r="H312" s="152"/>
+      <c r="I312" s="154"/>
+      <c r="J312" s="152"/>
+      <c r="K312" s="152"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="155" t="s">
         <v>8</v>
       </c>
-      <c r="B302" s="156" t="s">
-        <v>445</v>
-      </c>
-      <c r="C302" s="156" t="s">
-        <v>446</v>
-      </c>
-      <c r="D302" s="156" t="s">
+      <c r="B313" s="156" t="s">
+        <v>458</v>
+      </c>
+      <c r="C313" s="156" t="s">
+        <v>459</v>
+      </c>
+      <c r="D313" s="156" t="s">
         <v>146</v>
       </c>
-      <c r="E302" s="152"/>
-      <c r="F302" s="152"/>
-      <c r="G302" s="154"/>
-      <c r="H302" s="152"/>
-      <c r="I302" s="154"/>
-      <c r="J302" s="152"/>
-      <c r="K302" s="152"/>
-    </row>
-    <row r="303">
-      <c r="E303" s="152"/>
-      <c r="F303" s="152"/>
-      <c r="G303" s="154"/>
-      <c r="H303" s="152"/>
-      <c r="I303" s="154"/>
-      <c r="J303" s="152"/>
-      <c r="K303" s="152"/>
-    </row>
-    <row r="304">
-      <c r="A304" s="153"/>
-      <c r="B304" s="152"/>
-      <c r="C304" s="152"/>
-      <c r="D304" s="152"/>
-      <c r="E304" s="152"/>
-      <c r="F304" s="152"/>
-      <c r="G304" s="154"/>
-      <c r="H304" s="152"/>
-      <c r="I304" s="154"/>
-      <c r="J304" s="152"/>
-      <c r="K304" s="152"/>
+      <c r="E313" s="152"/>
+      <c r="F313" s="152"/>
+      <c r="G313" s="154"/>
+      <c r="H313" s="152"/>
+      <c r="I313" s="154"/>
+      <c r="J313" s="152"/>
+      <c r="K313" s="152"/>
+    </row>
+    <row r="314">
+      <c r="E314" s="152"/>
+      <c r="F314" s="152"/>
+      <c r="G314" s="154"/>
+      <c r="H314" s="152"/>
+      <c r="I314" s="154"/>
+      <c r="J314" s="152"/>
+      <c r="K314" s="152"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="153"/>
+      <c r="B315" s="152"/>
+      <c r="C315" s="152"/>
+      <c r="D315" s="152"/>
+      <c r="E315" s="152"/>
+      <c r="F315" s="152"/>
+      <c r="G315" s="154"/>
+      <c r="H315" s="152"/>
+      <c r="I315" s="154"/>
+      <c r="J315" s="152"/>
+      <c r="K315" s="152"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -10962,408 +11616,420 @@
         <v>133</v>
       </c>
       <c r="B1" s="158" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="C1" s="159" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="160" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="B2" s="161">
         <v>0.02</v>
       </c>
       <c r="C2" s="57" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="D2" s="162" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="163" t="s">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="B3" s="164">
         <v>0.02</v>
       </c>
       <c r="C3" s="165" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="D3" s="162" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="160" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="B4" s="161">
         <v>0.02</v>
       </c>
       <c r="C4" s="57" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="D4" s="162" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="163" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="B5" s="164">
         <v>0.02</v>
       </c>
       <c r="C5" s="166"/>
       <c r="D5" s="162" t="s">
-        <v>457</v>
+        <v>470</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="160" t="s">
-        <v>458</v>
+        <v>471</v>
       </c>
       <c r="B6" s="161">
         <v>0.02</v>
       </c>
       <c r="C6" s="167"/>
       <c r="D6" s="162" t="s">
-        <v>459</v>
+        <v>472</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="163" t="s">
-        <v>460</v>
+        <v>473</v>
       </c>
       <c r="B7" s="164">
         <v>0.02</v>
       </c>
       <c r="C7" s="166"/>
       <c r="D7" s="162" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="160" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="B8" s="161">
         <v>0.02</v>
       </c>
       <c r="C8" s="167"/>
       <c r="D8" s="162" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="163" t="s">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="B9" s="164">
         <v>0.02</v>
       </c>
       <c r="C9" s="165" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="D9" s="162" t="s">
-        <v>465</v>
+        <v>478</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="160" t="s">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="B10" s="161">
         <v>0.02</v>
       </c>
       <c r="C10" s="167"/>
       <c r="D10" s="162" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="163" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="B11" s="164">
         <v>0.02</v>
       </c>
       <c r="C11" s="166"/>
       <c r="D11" s="162" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="160" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="B12" s="161">
         <v>0.02</v>
       </c>
       <c r="C12" s="167"/>
       <c r="D12" s="162" t="s">
-        <v>471</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="163" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="B13" s="164">
         <v>0.02</v>
       </c>
-      <c r="C13" s="166"/>
+      <c r="C13" s="165" t="s">
+        <v>463</v>
+      </c>
       <c r="D13" s="162" t="s">
-        <v>473</v>
+        <v>486</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="160" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="B14" s="161">
         <v>0.02</v>
       </c>
       <c r="C14" s="57" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="D14" s="162" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="163" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="B15" s="164">
         <v>0.02</v>
       </c>
       <c r="C15" s="165" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="D15" s="162" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="160" t="s">
-        <v>478</v>
+        <v>491</v>
       </c>
       <c r="B16" s="161">
         <v>0.02</v>
       </c>
-      <c r="C16" s="167"/>
+      <c r="C16" s="57" t="s">
+        <v>463</v>
+      </c>
       <c r="D16" s="162" t="s">
-        <v>479</v>
+        <v>492</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="163" t="s">
-        <v>480</v>
+        <v>493</v>
       </c>
       <c r="B17" s="164">
         <v>0.01</v>
       </c>
       <c r="C17" s="165" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="D17" s="162" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="160" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="B18" s="161">
         <v>0.02</v>
       </c>
-      <c r="C18" s="167"/>
+      <c r="C18" s="57" t="s">
+        <v>463</v>
+      </c>
       <c r="D18" s="162" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="163" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="B19" s="164">
         <v>0.02</v>
       </c>
       <c r="C19" s="165" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="D19" s="162" t="s">
-        <v>485</v>
+        <v>498</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="160" t="s">
-        <v>486</v>
+        <v>499</v>
       </c>
       <c r="B20" s="161">
         <v>0.02</v>
       </c>
       <c r="C20" s="167"/>
       <c r="D20" s="162" t="s">
-        <v>487</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="163" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="B21" s="164">
         <v>0.02</v>
       </c>
       <c r="C21" s="166"/>
       <c r="D21" s="162" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="160" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="B22" s="161">
         <v>0.02</v>
       </c>
       <c r="C22" s="57" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="D22" s="162" t="s">
-        <v>491</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="163" t="s">
-        <v>492</v>
+        <v>505</v>
       </c>
       <c r="B23" s="164">
         <v>0.02</v>
       </c>
       <c r="C23" s="166"/>
       <c r="D23" s="162" t="s">
-        <v>493</v>
+        <v>506</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="160" t="s">
-        <v>494</v>
+        <v>507</v>
       </c>
       <c r="B24" s="161">
         <v>0.02</v>
       </c>
       <c r="C24" s="167"/>
       <c r="D24" s="162" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="163" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="B25" s="164">
         <v>0.02</v>
       </c>
       <c r="C25" s="165" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="D25" s="162" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="160" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="B26" s="161">
         <v>0.02</v>
       </c>
-      <c r="C26" s="167"/>
+      <c r="C26" s="57" t="s">
+        <v>463</v>
+      </c>
       <c r="D26" s="162" t="s">
-        <v>499</v>
+        <v>512</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="163" t="s">
-        <v>500</v>
+        <v>513</v>
       </c>
       <c r="B27" s="164">
         <v>0.02</v>
       </c>
-      <c r="C27" s="166"/>
+      <c r="C27" s="165" t="s">
+        <v>463</v>
+      </c>
       <c r="D27" s="162" t="s">
-        <v>501</v>
+        <v>514</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="160" t="s">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="B28" s="161">
         <v>0.02</v>
       </c>
-      <c r="C28" s="167"/>
+      <c r="C28" s="57" t="s">
+        <v>463</v>
+      </c>
       <c r="D28" s="162" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="163" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="B29" s="164">
         <v>0.02</v>
       </c>
       <c r="C29" s="165" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="D29" s="162" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="160" t="s">
-        <v>506</v>
+        <v>519</v>
       </c>
       <c r="B30" s="161">
         <v>0.02</v>
       </c>
       <c r="C30" s="57" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="D30" s="162" t="s">
-        <v>507</v>
+        <v>520</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="163" t="s">
-        <v>508</v>
+        <v>521</v>
       </c>
       <c r="B31" s="164">
         <v>0.01</v>
       </c>
       <c r="C31" s="166"/>
       <c r="D31" s="162" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="168" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="B32" s="169">
         <v>0.02</v>
       </c>
       <c r="C32" s="170" t="s">
-        <v>450</v>
+        <v>463</v>
       </c>
       <c r="D32" s="162" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
     </row>
     <row r="33">
